--- a/data/output/sim_gridrnd/ABS1/group_520_40/results/ABS1_G8_results_summary.xlsx
+++ b/data/output/sim_gridrnd/ABS1/group_520_40/results/ABS1_G8_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,860 +466,981 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S02_G8_518_39_ABS1</t>
+          <t>S01_G8_520_40_ABS1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>59.30318754633062</v>
       </c>
       <c r="D2" t="n">
-        <v>57.82060785767235</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F2" t="n">
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>70.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>539.1232947511347</v>
-      </c>
-      <c r="J2" t="n">
-        <v>33.75502996136742</v>
-      </c>
-      <c r="K2" t="n">
-        <v>532.7753689263266</v>
-      </c>
-      <c r="L2" t="n">
-        <v>38.02524566133652</v>
-      </c>
-      <c r="M2" t="n">
-        <v>530.0039468664742</v>
-      </c>
-      <c r="N2" t="n">
-        <v>43.6254316896086</v>
-      </c>
-      <c r="O2" t="n">
-        <v>527.0044643312627</v>
-      </c>
-      <c r="P2" t="n">
-        <v>40.73825602426105</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>528.7694041180564</v>
-      </c>
       <c r="R2" t="n">
-        <v>41.89074866731599</v>
+        <v>540.6900000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>525.2850975421301</v>
+        <v>20.83</v>
       </c>
       <c r="T2" t="n">
-        <v>43.547596286355</v>
+        <v>539.85</v>
       </c>
       <c r="U2" t="n">
-        <v>526.0563208067924</v>
+        <v>23.52</v>
       </c>
       <c r="V2" t="n">
-        <v>44.71880272783581</v>
+        <v>530.6</v>
       </c>
       <c r="W2" t="n">
-        <v>525.2793754071585</v>
+        <v>41.62</v>
       </c>
       <c r="X2" t="n">
-        <v>42.68300279399323</v>
+        <v>531.21</v>
       </c>
       <c r="Y2" t="n">
-        <v>524.1866329354004</v>
+        <v>38.77</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.96576952216089</v>
+        <v>531.39</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.8</v>
+        <v>40.61</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.7966101694915254</v>
+        <v>529.39</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.6623376623376623</v>
+        <v>45.76</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4432989690721649</v>
+        <v>527.88</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3675213675213675</v>
+        <v>42.32</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2846715328467153</v>
+        <v>526.55</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2611464968152866</v>
+        <v>42.87</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.2203389830508475</v>
+        <v>524.1900000000001</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.2081218274111675</v>
+        <v>43.48</v>
       </c>
       <c r="AJ2" t="n">
-        <v>556.075</v>
+        <v>0.9</v>
       </c>
       <c r="AK2" t="n">
-        <v>547.4166666666666</v>
+        <v>0.9322033898305084</v>
       </c>
       <c r="AL2" t="n">
-        <v>541.7</v>
+        <v>0.7402597402597403</v>
       </c>
       <c r="AM2" t="n">
-        <v>535.17</v>
+        <v>0.5257731958762887</v>
       </c>
       <c r="AN2" t="n">
-        <v>534.1</v>
+        <v>0.4358974358974359</v>
       </c>
       <c r="AO2" t="n">
-        <v>531.35</v>
+        <v>0.3576642335766423</v>
       </c>
       <c r="AP2" t="n">
-        <v>531.24375</v>
+        <v>0.286624203821656</v>
       </c>
       <c r="AQ2" t="n">
-        <v>530.0444444444445</v>
+        <v>0.231638418079096</v>
       </c>
       <c r="AR2" t="n">
-        <v>530.2</v>
+        <v>0.1979695431472081</v>
       </c>
       <c r="AS2" t="n">
-        <v>51.97806628761789</v>
+        <v>542.775</v>
       </c>
       <c r="AT2" t="n">
-        <v>46.81641153365867</v>
+        <v>540.2833333333333</v>
       </c>
       <c r="AU2" t="n">
-        <v>45.84195676451868</v>
+        <v>532.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>47.07803203193608</v>
+        <v>527.72</v>
       </c>
       <c r="AW2" t="n">
-        <v>46.29982001404901</v>
+        <v>528.5666666666667</v>
       </c>
       <c r="AX2" t="n">
-        <v>46.76352745463071</v>
+        <v>528.2428571428571</v>
       </c>
       <c r="AY2" t="n">
-        <v>46.28589780848482</v>
+        <v>527.2125</v>
       </c>
       <c r="AZ2" t="n">
-        <v>46.20002672224122</v>
+        <v>526.1611111111112</v>
       </c>
       <c r="BA2" t="n">
-        <v>45.53668850498464</v>
+        <v>525.8150000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>480</v>
+        <v>24.97047005965246</v>
       </c>
       <c r="BC2" t="n">
-        <v>480</v>
+        <v>25.22636958070309</v>
       </c>
       <c r="BD2" t="n">
-        <v>480</v>
+        <v>28.2981448155175</v>
       </c>
       <c r="BE2" t="n">
-        <v>464</v>
+        <v>36.85595745602059</v>
       </c>
       <c r="BF2" t="n">
-        <v>464</v>
+        <v>40.39734589741702</v>
       </c>
       <c r="BG2" t="n">
-        <v>464</v>
+        <v>42.60782480594236</v>
       </c>
       <c r="BH2" t="n">
-        <v>463</v>
+        <v>43.56695816499013</v>
       </c>
       <c r="BI2" t="n">
-        <v>463</v>
+        <v>43.93342993020347</v>
       </c>
       <c r="BJ2" t="n">
-        <v>463</v>
+        <v>43.9013755479256</v>
       </c>
       <c r="BK2" t="n">
-        <v>717</v>
+        <v>492</v>
       </c>
       <c r="BL2" t="n">
-        <v>717</v>
+        <v>492</v>
       </c>
       <c r="BM2" t="n">
-        <v>717</v>
+        <v>479</v>
       </c>
       <c r="BN2" t="n">
-        <v>717</v>
+        <v>452</v>
       </c>
       <c r="BO2" t="n">
-        <v>717</v>
+        <v>452</v>
       </c>
       <c r="BP2" t="n">
-        <v>717</v>
+        <v>452</v>
       </c>
       <c r="BQ2" t="n">
-        <v>717</v>
+        <v>452</v>
       </c>
       <c r="BR2" t="n">
-        <v>717</v>
+        <v>452</v>
       </c>
       <c r="BS2" t="n">
-        <v>717</v>
+        <v>452</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.5</v>
+        <v>643</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.5</v>
+        <v>643</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.9166666666666666</v>
+        <v>643</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.0625</v>
+        <v>643</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.9523809523809523</v>
+        <v>643</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.03703703703703703</v>
+        <v>643</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.8484848484848485</v>
+        <v>643</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.8888888888888888</v>
+        <v>643</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.8636363636363636</v>
+        <v>643</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>524.1900000000001</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>43.48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S01_G8_520_40_ABS1</t>
+          <t>S02_G8_518_39_ABS1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>57.82060785767235</v>
       </c>
       <c r="D3" t="n">
-        <v>59.30318754633062</v>
+        <v>39</v>
       </c>
       <c r="E3" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F3" t="n">
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>72.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>540.6882823598943</v>
-      </c>
-      <c r="J3" t="n">
-        <v>20.83493673636485</v>
-      </c>
-      <c r="K3" t="n">
-        <v>539.8461689537596</v>
-      </c>
-      <c r="L3" t="n">
-        <v>23.51967755731748</v>
-      </c>
-      <c r="M3" t="n">
-        <v>530.5977117854969</v>
-      </c>
-      <c r="N3" t="n">
-        <v>41.61524093770942</v>
-      </c>
-      <c r="O3" t="n">
-        <v>531.2117592455265</v>
-      </c>
-      <c r="P3" t="n">
-        <v>38.76622433157516</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>531.3885697033245</v>
-      </c>
       <c r="R3" t="n">
-        <v>40.60655537102357</v>
+        <v>539.12</v>
       </c>
       <c r="S3" t="n">
-        <v>529.3942597322282</v>
+        <v>33.76</v>
       </c>
       <c r="T3" t="n">
-        <v>45.76481077977019</v>
+        <v>532.78</v>
       </c>
       <c r="U3" t="n">
-        <v>527.8832542358253</v>
+        <v>38.03</v>
       </c>
       <c r="V3" t="n">
-        <v>42.32146238449552</v>
+        <v>530</v>
       </c>
       <c r="W3" t="n">
-        <v>526.5450298949231</v>
+        <v>43.63</v>
       </c>
       <c r="X3" t="n">
-        <v>42.87077129024063</v>
+        <v>527</v>
       </c>
       <c r="Y3" t="n">
-        <v>524.1900558654104</v>
+        <v>40.74</v>
       </c>
       <c r="Z3" t="n">
-        <v>43.47884109054702</v>
+        <v>528.77</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.9</v>
+        <v>41.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9322033898305084</v>
+        <v>525.29</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7402597402597403</v>
+        <v>43.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5257731958762887</v>
+        <v>526.0599999999999</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.4358974358974359</v>
+        <v>44.72</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3576642335766423</v>
+        <v>525.28</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.286624203821656</v>
+        <v>42.68</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.231638418079096</v>
+        <v>524.1900000000001</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1979695431472081</v>
+        <v>40.97</v>
       </c>
       <c r="AJ3" t="n">
-        <v>542.775</v>
+        <v>0.8</v>
       </c>
       <c r="AK3" t="n">
-        <v>540.2833333333333</v>
+        <v>0.7966101694915254</v>
       </c>
       <c r="AL3" t="n">
-        <v>532.8</v>
+        <v>0.6623376623376623</v>
       </c>
       <c r="AM3" t="n">
-        <v>527.72</v>
+        <v>0.4432989690721649</v>
       </c>
       <c r="AN3" t="n">
-        <v>528.5666666666667</v>
+        <v>0.3675213675213675</v>
       </c>
       <c r="AO3" t="n">
-        <v>528.2428571428571</v>
+        <v>0.2846715328467153</v>
       </c>
       <c r="AP3" t="n">
-        <v>527.2125</v>
+        <v>0.2611464968152866</v>
       </c>
       <c r="AQ3" t="n">
-        <v>526.1611111111112</v>
+        <v>0.2203389830508475</v>
       </c>
       <c r="AR3" t="n">
-        <v>525.8150000000001</v>
+        <v>0.2081218274111675</v>
       </c>
       <c r="AS3" t="n">
-        <v>24.97047005965246</v>
+        <v>556.075</v>
       </c>
       <c r="AT3" t="n">
-        <v>25.22636958070309</v>
+        <v>547.4166666666666</v>
       </c>
       <c r="AU3" t="n">
-        <v>28.2981448155175</v>
+        <v>541.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>36.85595745602059</v>
+        <v>535.17</v>
       </c>
       <c r="AW3" t="n">
-        <v>40.39734589741702</v>
+        <v>534.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>42.60782480594236</v>
+        <v>531.35</v>
       </c>
       <c r="AY3" t="n">
-        <v>43.56695816499013</v>
+        <v>531.24375</v>
       </c>
       <c r="AZ3" t="n">
-        <v>43.93342993020347</v>
+        <v>530.0444444444445</v>
       </c>
       <c r="BA3" t="n">
-        <v>43.9013755479256</v>
+        <v>530.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>492</v>
+        <v>51.97806628761789</v>
       </c>
       <c r="BC3" t="n">
-        <v>492</v>
+        <v>46.81641153365867</v>
       </c>
       <c r="BD3" t="n">
-        <v>479</v>
+        <v>45.84195676451868</v>
       </c>
       <c r="BE3" t="n">
-        <v>452</v>
+        <v>47.07803203193608</v>
       </c>
       <c r="BF3" t="n">
-        <v>452</v>
+        <v>46.29982001404901</v>
       </c>
       <c r="BG3" t="n">
-        <v>452</v>
+        <v>46.76352745463071</v>
       </c>
       <c r="BH3" t="n">
-        <v>452</v>
+        <v>46.28589780848482</v>
       </c>
       <c r="BI3" t="n">
-        <v>452</v>
+        <v>46.20002672224122</v>
       </c>
       <c r="BJ3" t="n">
-        <v>452</v>
+        <v>45.53668850498464</v>
       </c>
       <c r="BK3" t="n">
-        <v>643</v>
+        <v>480</v>
       </c>
       <c r="BL3" t="n">
-        <v>643</v>
+        <v>480</v>
       </c>
       <c r="BM3" t="n">
-        <v>643</v>
+        <v>480</v>
       </c>
       <c r="BN3" t="n">
-        <v>643</v>
+        <v>464</v>
       </c>
       <c r="BO3" t="n">
-        <v>643</v>
+        <v>464</v>
       </c>
       <c r="BP3" t="n">
-        <v>643</v>
+        <v>464</v>
       </c>
       <c r="BQ3" t="n">
-        <v>643</v>
+        <v>463</v>
       </c>
       <c r="BR3" t="n">
-        <v>643</v>
+        <v>463</v>
       </c>
       <c r="BS3" t="n">
-        <v>643</v>
+        <v>463</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.25</v>
+        <v>717</v>
       </c>
       <c r="BU3" t="n">
-        <v>1</v>
+        <v>717</v>
       </c>
       <c r="BV3" t="n">
-        <v>1</v>
+        <v>717</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.9090909090909091</v>
+        <v>717</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.8181818181818182</v>
+        <v>717</v>
       </c>
       <c r="BY3" t="n">
-        <v>1</v>
+        <v>717</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.9333333333333333</v>
+        <v>717</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.8421052631578947</v>
+        <v>717</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.4583333333333333</v>
+        <v>717</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.8636363636363636</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>524.1900000000001</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>40.97</v>
       </c>
     </row>
     <row r="4">
@@ -1332,10 +1453,10 @@
         <v>521</v>
       </c>
       <c r="C4" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D4" t="n">
         <v>41</v>
-      </c>
-      <c r="D4" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E4" t="n">
         <v>521</v>
@@ -1344,736 +1465,835 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>528.9424336933528</v>
-      </c>
-      <c r="J4" t="n">
-        <v>25.30455820861904</v>
-      </c>
-      <c r="K4" t="n">
-        <v>528.1048054621656</v>
-      </c>
-      <c r="L4" t="n">
-        <v>44.8243760943575</v>
-      </c>
-      <c r="M4" t="n">
-        <v>523.0577880050744</v>
-      </c>
-      <c r="N4" t="n">
-        <v>46.45789358761446</v>
-      </c>
-      <c r="O4" t="n">
-        <v>523.1662667590231</v>
-      </c>
-      <c r="P4" t="n">
-        <v>54.54157289204588</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>522.2952754772992</v>
-      </c>
       <c r="R4" t="n">
-        <v>46.19636051761744</v>
+        <v>528.9400000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>521.6365795450614</v>
+        <v>25.3</v>
       </c>
       <c r="T4" t="n">
-        <v>47.46253688527344</v>
+        <v>528.1</v>
       </c>
       <c r="U4" t="n">
-        <v>519.6854844529024</v>
+        <v>44.82</v>
       </c>
       <c r="V4" t="n">
-        <v>48.84080139294998</v>
+        <v>523.0599999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>519.1339493745094</v>
+        <v>46.46</v>
       </c>
       <c r="X4" t="n">
-        <v>43.4962475510887</v>
+        <v>523.17</v>
       </c>
       <c r="Y4" t="n">
-        <v>518.4985557182611</v>
+        <v>54.54</v>
       </c>
       <c r="Z4" t="n">
-        <v>43.78477821995585</v>
+        <v>522.3</v>
       </c>
       <c r="AA4" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>521.64</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>519.6900000000001</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>48.84</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>519.13</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>518.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>43.78</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>0.6</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AK4" t="n">
         <v>0.4666666666666667</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AL4" t="n">
         <v>0.225</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AM4" t="n">
         <v>0.18</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AN4" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AO4" t="n">
         <v>0.1</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AP4" t="n">
         <v>0.075</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AQ4" t="n">
         <v>0.07777777777777778</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AR4" t="n">
         <v>0.08</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AS4" t="n">
         <v>531.25</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AT4" t="n">
         <v>534.7666666666667</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AU4" t="n">
         <v>523.6</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AV4" t="n">
         <v>523.59</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AW4" t="n">
         <v>522.9416666666667</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AX4" t="n">
         <v>522.3571428571429</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AY4" t="n">
         <v>521.79375</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AZ4" t="n">
         <v>522.0777777777778</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="BA4" t="n">
         <v>522.05</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="BB4" t="n">
         <v>33.55797222717726</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="BC4" t="n">
         <v>39.78415374101715</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="BD4" t="n">
         <v>48.32561432615213</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="BE4" t="n">
         <v>50.58222909283457</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="BF4" t="n">
         <v>51.18923972759205</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BG4" t="n">
         <v>50.61917640981689</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BH4" t="n">
         <v>49.99851208723616</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BI4" t="n">
         <v>49.53533593479345</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BJ4" t="n">
         <v>48.27657299353383</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BK4" t="n">
         <v>483</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BL4" t="n">
         <v>468</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BM4" t="n">
         <v>439</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BN4" t="n">
         <v>439</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BO4" t="n">
         <v>439</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BP4" t="n">
         <v>439</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BQ4" t="n">
         <v>439</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BR4" t="n">
         <v>439</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BS4" t="n">
         <v>439</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="BT4" t="n">
         <v>655</v>
       </c>
-      <c r="BL4" t="n">
+      <c r="BU4" t="n">
         <v>655</v>
       </c>
-      <c r="BM4" t="n">
+      <c r="BV4" t="n">
         <v>655</v>
       </c>
-      <c r="BN4" t="n">
+      <c r="BW4" t="n">
         <v>655</v>
       </c>
-      <c r="BO4" t="n">
+      <c r="BX4" t="n">
         <v>655</v>
       </c>
-      <c r="BP4" t="n">
+      <c r="BY4" t="n">
         <v>655</v>
       </c>
-      <c r="BQ4" t="n">
+      <c r="BZ4" t="n">
         <v>655</v>
       </c>
-      <c r="BR4" t="n">
+      <c r="CA4" t="n">
         <v>655</v>
       </c>
-      <c r="BS4" t="n">
+      <c r="CB4" t="n">
         <v>655</v>
       </c>
-      <c r="BT4" t="n">
+      <c r="CC4" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="CD4" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV4" t="n">
+      <c r="CE4" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BW4" t="n">
+      <c r="CF4" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="CG4" t="n">
         <v>1</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="CH4" t="n">
         <v>0.9047619047619048</v>
       </c>
-      <c r="BZ4" t="n">
+      <c r="CI4" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CJ4" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="CB4" t="n">
+      <c r="CK4" t="n">
         <v>1</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>518.5</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>43.78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S06_G8_520_40_ABS1</t>
+          <t>S04_G8_518_40_ABS1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C5" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D5" t="n">
         <v>40</v>
       </c>
-      <c r="D5" t="n">
-        <v>59.30318754633062</v>
-      </c>
       <c r="E5" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F5" t="n">
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>514.5403258839211</v>
-      </c>
-      <c r="J5" t="n">
-        <v>44.20142410018578</v>
-      </c>
-      <c r="K5" t="n">
-        <v>516.4986630419987</v>
-      </c>
-      <c r="L5" t="n">
-        <v>41.16015319596695</v>
-      </c>
-      <c r="M5" t="n">
-        <v>524.1612218310582</v>
-      </c>
-      <c r="N5" t="n">
-        <v>40.25813060732517</v>
-      </c>
-      <c r="O5" t="n">
-        <v>526.5637226962325</v>
-      </c>
-      <c r="P5" t="n">
-        <v>39.69863422884843</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>527.754141919872</v>
-      </c>
       <c r="R5" t="n">
-        <v>38.59659144940449</v>
+        <v>504.91</v>
       </c>
       <c r="S5" t="n">
-        <v>526.1056611169337</v>
+        <v>53.6</v>
       </c>
       <c r="T5" t="n">
-        <v>36.67305765892985</v>
+        <v>501.26</v>
       </c>
       <c r="U5" t="n">
-        <v>523.3944157079113</v>
+        <v>44.85</v>
       </c>
       <c r="V5" t="n">
-        <v>40.21882087566467</v>
+        <v>506.15</v>
       </c>
       <c r="W5" t="n">
-        <v>525.3116854730295</v>
+        <v>42.14</v>
       </c>
       <c r="X5" t="n">
-        <v>39.4039755117121</v>
+        <v>502.21</v>
       </c>
       <c r="Y5" t="n">
-        <v>520.4930769923279</v>
+        <v>44.61</v>
       </c>
       <c r="Z5" t="n">
-        <v>42.009771348725</v>
+        <v>505.27</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.15</v>
+        <v>44.96</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1</v>
+        <v>506.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.125</v>
+        <v>44.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.18</v>
+        <v>504.68</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.2100840336134454</v>
+        <v>42.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2517985611510791</v>
+        <v>505.92</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2327044025157233</v>
+        <v>41.62</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.2290502793296089</v>
+        <v>503.81</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.1758793969849246</v>
+        <v>42.54</v>
       </c>
       <c r="AJ5" t="n">
-        <v>515.25</v>
+        <v>-0.02564102564102564</v>
       </c>
       <c r="AK5" t="n">
-        <v>516.8166666666667</v>
+        <v>-0.05084745762711865</v>
       </c>
       <c r="AL5" t="n">
-        <v>519.5625</v>
+        <v>-0.01265822784810127</v>
       </c>
       <c r="AM5" t="n">
-        <v>521.02</v>
+        <v>-0.0303030303030303</v>
       </c>
       <c r="AN5" t="n">
-        <v>523.1083333333333</v>
+        <v>-0.008403361344537815</v>
       </c>
       <c r="AO5" t="n">
-        <v>523.5285714285715</v>
+        <v>-0.02158273381294964</v>
       </c>
       <c r="AP5" t="n">
-        <v>523.25625</v>
+        <v>-0.01886792452830189</v>
       </c>
       <c r="AQ5" t="n">
-        <v>524.1166666666667</v>
+        <v>-0.01675977653631285</v>
       </c>
       <c r="AR5" t="n">
-        <v>522.375</v>
+        <v>-0.01507537688442211</v>
       </c>
       <c r="AS5" t="n">
-        <v>51.61140862251291</v>
+        <v>503.575</v>
       </c>
       <c r="AT5" t="n">
-        <v>48.2495221622856</v>
+        <v>500.8666666666667</v>
       </c>
       <c r="AU5" t="n">
-        <v>46.84785047096612</v>
+        <v>502.6875</v>
       </c>
       <c r="AV5" t="n">
-        <v>44.48662270840529</v>
+        <v>501.81</v>
       </c>
       <c r="AW5" t="n">
-        <v>43.80692407853149</v>
+        <v>503.0166666666667</v>
       </c>
       <c r="AX5" t="n">
-        <v>42.43254190176329</v>
+        <v>502.85</v>
       </c>
       <c r="AY5" t="n">
-        <v>41.98455770801331</v>
+        <v>503.15</v>
       </c>
       <c r="AZ5" t="n">
-        <v>41.65230085681542</v>
+        <v>503.4777777777778</v>
       </c>
       <c r="BA5" t="n">
-        <v>42.14017530813084</v>
+        <v>503.56</v>
       </c>
       <c r="BB5" t="n">
-        <v>437</v>
+        <v>55.35606899880084</v>
       </c>
       <c r="BC5" t="n">
-        <v>437</v>
+        <v>54.32693213826413</v>
       </c>
       <c r="BD5" t="n">
-        <v>437</v>
+        <v>51.60295382776067</v>
       </c>
       <c r="BE5" t="n">
-        <v>437</v>
+        <v>49.98153559065587</v>
       </c>
       <c r="BF5" t="n">
-        <v>437</v>
+        <v>49.72021442252861</v>
       </c>
       <c r="BG5" t="n">
-        <v>437</v>
+        <v>48.81875005715384</v>
       </c>
       <c r="BH5" t="n">
-        <v>437</v>
+        <v>47.7870536861188</v>
       </c>
       <c r="BI5" t="n">
-        <v>437</v>
+        <v>46.87032412892637</v>
       </c>
       <c r="BJ5" t="n">
-        <v>437</v>
+        <v>46.20136794511608</v>
       </c>
       <c r="BK5" t="n">
-        <v>643</v>
+        <v>348</v>
       </c>
       <c r="BL5" t="n">
-        <v>643</v>
+        <v>348</v>
       </c>
       <c r="BM5" t="n">
-        <v>643</v>
+        <v>348</v>
       </c>
       <c r="BN5" t="n">
-        <v>643</v>
+        <v>348</v>
       </c>
       <c r="BO5" t="n">
-        <v>643</v>
+        <v>348</v>
       </c>
       <c r="BP5" t="n">
-        <v>643</v>
+        <v>348</v>
       </c>
       <c r="BQ5" t="n">
-        <v>643</v>
+        <v>348</v>
       </c>
       <c r="BR5" t="n">
-        <v>643</v>
+        <v>348</v>
       </c>
       <c r="BS5" t="n">
-        <v>643</v>
+        <v>348</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.6</v>
+        <v>615</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.6</v>
+        <v>615</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.8181818181818182</v>
+        <v>615</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.8571428571428571</v>
+        <v>615</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.8421052631578947</v>
+        <v>615</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.9090909090909091</v>
+        <v>615</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.9583333333333334</v>
+        <v>615</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.9615384615384616</v>
+        <v>615</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.9285714285714286</v>
+        <v>615</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.9722222222222222</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>503.81</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>42.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S04_G8_518_40_ABS1</t>
+          <t>S05_G8_520_40_ABS1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C6" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D6" t="n">
         <v>40</v>
       </c>
-      <c r="D6" t="n">
-        <v>59.30318754633062</v>
-      </c>
       <c r="E6" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F6" t="n">
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>72</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>504.9144612471828</v>
-      </c>
-      <c r="J6" t="n">
-        <v>53.60114054642959</v>
-      </c>
-      <c r="K6" t="n">
-        <v>501.260950380622</v>
-      </c>
-      <c r="L6" t="n">
-        <v>44.85318677722479</v>
-      </c>
-      <c r="M6" t="n">
-        <v>506.1509199328775</v>
-      </c>
-      <c r="N6" t="n">
-        <v>42.13709226258518</v>
-      </c>
-      <c r="O6" t="n">
-        <v>502.2074815866458</v>
-      </c>
-      <c r="P6" t="n">
-        <v>44.60772098200839</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>505.2700675011891</v>
-      </c>
       <c r="R6" t="n">
-        <v>44.96396051468239</v>
+        <v>527.85</v>
       </c>
       <c r="S6" t="n">
-        <v>506.029043667278</v>
+        <v>43.9</v>
       </c>
       <c r="T6" t="n">
-        <v>44.61776040456565</v>
+        <v>526.78</v>
       </c>
       <c r="U6" t="n">
-        <v>504.6778811405337</v>
+        <v>35.35</v>
       </c>
       <c r="V6" t="n">
-        <v>42.11278437988771</v>
+        <v>522.46</v>
       </c>
       <c r="W6" t="n">
-        <v>505.9157481534448</v>
+        <v>34.38</v>
       </c>
       <c r="X6" t="n">
-        <v>41.61924319201596</v>
+        <v>525.42</v>
       </c>
       <c r="Y6" t="n">
-        <v>503.8114263199248</v>
+        <v>34.59</v>
       </c>
       <c r="Z6" t="n">
-        <v>42.53743884096056</v>
+        <v>527.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.02564102564102564</v>
+        <v>33.51</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.05084745762711865</v>
+        <v>527.8200000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.01265822784810127</v>
+        <v>37.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.0303030303030303</v>
+        <v>523.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.008403361344537815</v>
+        <v>40.04</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.02158273381294964</v>
+        <v>521.34</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.01886792452830189</v>
+        <v>38.61</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.01675977653631285</v>
+        <v>525.23</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.01507537688442211</v>
+        <v>40.76</v>
       </c>
       <c r="AJ6" t="n">
-        <v>503.575</v>
+        <v>0.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>500.8666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="AL6" t="n">
-        <v>502.6875</v>
+        <v>0.2151898734177215</v>
       </c>
       <c r="AM6" t="n">
-        <v>501.81</v>
+        <v>0.2525252525252525</v>
       </c>
       <c r="AN6" t="n">
-        <v>503.0166666666667</v>
+        <v>0.2605042016806723</v>
       </c>
       <c r="AO6" t="n">
-        <v>502.85</v>
+        <v>0.2661870503597122</v>
       </c>
       <c r="AP6" t="n">
-        <v>503.15</v>
+        <v>0.2278481012658228</v>
       </c>
       <c r="AQ6" t="n">
-        <v>503.4777777777778</v>
+        <v>0.1910112359550562</v>
       </c>
       <c r="AR6" t="n">
-        <v>503.56</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="AS6" t="n">
-        <v>55.35606899880084</v>
+        <v>527.475</v>
       </c>
       <c r="AT6" t="n">
-        <v>54.32693213826413</v>
+        <v>524.4166666666666</v>
       </c>
       <c r="AU6" t="n">
-        <v>51.60295382776067</v>
+        <v>524.7125</v>
       </c>
       <c r="AV6" t="n">
-        <v>49.98153559065587</v>
+        <v>525.54</v>
       </c>
       <c r="AW6" t="n">
-        <v>49.72021442252861</v>
+        <v>525.9583333333334</v>
       </c>
       <c r="AX6" t="n">
-        <v>48.81875005715384</v>
+        <v>526.5571428571428</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.7870536861188</v>
+        <v>526.1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>46.87032412892637</v>
+        <v>525.2777777777778</v>
       </c>
       <c r="BA6" t="n">
-        <v>46.20136794511608</v>
+        <v>525.26</v>
       </c>
       <c r="BB6" t="n">
-        <v>348</v>
+        <v>47.07758888260953</v>
       </c>
       <c r="BC6" t="n">
-        <v>348</v>
+        <v>44.15174276162708</v>
       </c>
       <c r="BD6" t="n">
-        <v>348</v>
+        <v>41.11088473567554</v>
       </c>
       <c r="BE6" t="n">
-        <v>348</v>
+        <v>39.83476371211457</v>
       </c>
       <c r="BF6" t="n">
-        <v>348</v>
+        <v>39.29109225454996</v>
       </c>
       <c r="BG6" t="n">
-        <v>348</v>
+        <v>39.28817914345438</v>
       </c>
       <c r="BH6" t="n">
-        <v>348</v>
+        <v>39.46203872077569</v>
       </c>
       <c r="BI6" t="n">
-        <v>348</v>
+        <v>39.70685017244863</v>
       </c>
       <c r="BJ6" t="n">
-        <v>348</v>
+        <v>39.92508484649719</v>
       </c>
       <c r="BK6" t="n">
-        <v>615</v>
+        <v>447</v>
       </c>
       <c r="BL6" t="n">
-        <v>615</v>
+        <v>447</v>
       </c>
       <c r="BM6" t="n">
-        <v>615</v>
+        <v>447</v>
       </c>
       <c r="BN6" t="n">
-        <v>615</v>
+        <v>447</v>
       </c>
       <c r="BO6" t="n">
-        <v>615</v>
+        <v>447</v>
       </c>
       <c r="BP6" t="n">
-        <v>615</v>
+        <v>447</v>
       </c>
       <c r="BQ6" t="n">
-        <v>615</v>
+        <v>447</v>
       </c>
       <c r="BR6" t="n">
-        <v>615</v>
+        <v>447</v>
       </c>
       <c r="BS6" t="n">
-        <v>615</v>
+        <v>447</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.8333333333333334</v>
+        <v>646</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.9</v>
+        <v>646</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.8461538461538461</v>
+        <v>646</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.3571428571428572</v>
+        <v>646</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.2380952380952381</v>
+        <v>646</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.9629629629629629</v>
+        <v>646</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.967741935483871</v>
+        <v>646</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.9722222222222222</v>
+        <v>646</v>
       </c>
       <c r="CB6" t="n">
+        <v>646</v>
+      </c>
+      <c r="CC6" t="n">
         <v>1</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>525.23</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>40.76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S05_G8_520_40_ABS1</t>
+          <t>S06_G8_520_40_ABS1</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>520</v>
       </c>
       <c r="C7" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D7" t="n">
         <v>40</v>
-      </c>
-      <c r="D7" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E7" t="n">
         <v>520</v>
@@ -2082,720 +2302,819 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>74</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>527.8536678287211</v>
-      </c>
-      <c r="J7" t="n">
-        <v>43.90197384986524</v>
-      </c>
-      <c r="K7" t="n">
-        <v>526.7780456978036</v>
-      </c>
-      <c r="L7" t="n">
-        <v>35.34934309727134</v>
-      </c>
-      <c r="M7" t="n">
-        <v>522.4617764697051</v>
-      </c>
-      <c r="N7" t="n">
-        <v>34.38155139410341</v>
-      </c>
-      <c r="O7" t="n">
-        <v>525.4170229494766</v>
-      </c>
-      <c r="P7" t="n">
-        <v>34.58536093246938</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>527.1701841436105</v>
-      </c>
       <c r="R7" t="n">
-        <v>33.50923236563924</v>
+        <v>514.54</v>
       </c>
       <c r="S7" t="n">
-        <v>527.8182852413897</v>
+        <v>44.2</v>
       </c>
       <c r="T7" t="n">
-        <v>37.09600279676235</v>
+        <v>516.5</v>
       </c>
       <c r="U7" t="n">
-        <v>523.9012996920919</v>
+        <v>41.16</v>
       </c>
       <c r="V7" t="n">
-        <v>40.0371171931225</v>
+        <v>524.16</v>
       </c>
       <c r="W7" t="n">
-        <v>521.3430039031255</v>
+        <v>40.26</v>
       </c>
       <c r="X7" t="n">
-        <v>38.61165743142817</v>
+        <v>526.5599999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>525.2288823676208</v>
+        <v>39.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>40.75648978252738</v>
+        <v>527.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.25</v>
+        <v>38.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2333333333333333</v>
+        <v>526.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2151898734177215</v>
+        <v>36.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.2525252525252525</v>
+        <v>523.39</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.2605042016806723</v>
+        <v>40.22</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2661870503597122</v>
+        <v>525.3099999999999</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.2278481012658228</v>
+        <v>39.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1910112359550562</v>
+        <v>520.49</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.1818181818181818</v>
+        <v>42.01</v>
       </c>
       <c r="AJ7" t="n">
-        <v>527.475</v>
+        <v>0.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>524.4166666666666</v>
+        <v>0.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>524.7125</v>
+        <v>0.125</v>
       </c>
       <c r="AM7" t="n">
-        <v>525.54</v>
+        <v>0.18</v>
       </c>
       <c r="AN7" t="n">
-        <v>525.9583333333334</v>
+        <v>0.2100840336134454</v>
       </c>
       <c r="AO7" t="n">
-        <v>526.5571428571428</v>
+        <v>0.2517985611510791</v>
       </c>
       <c r="AP7" t="n">
-        <v>526.1</v>
+        <v>0.2327044025157233</v>
       </c>
       <c r="AQ7" t="n">
-        <v>525.2777777777778</v>
+        <v>0.2290502793296089</v>
       </c>
       <c r="AR7" t="n">
-        <v>525.26</v>
+        <v>0.1758793969849246</v>
       </c>
       <c r="AS7" t="n">
-        <v>47.07758888260953</v>
+        <v>515.25</v>
       </c>
       <c r="AT7" t="n">
-        <v>44.15174276162708</v>
+        <v>516.8166666666667</v>
       </c>
       <c r="AU7" t="n">
-        <v>41.11088473567554</v>
+        <v>519.5625</v>
       </c>
       <c r="AV7" t="n">
-        <v>39.83476371211457</v>
+        <v>521.02</v>
       </c>
       <c r="AW7" t="n">
-        <v>39.29109225454996</v>
+        <v>523.1083333333333</v>
       </c>
       <c r="AX7" t="n">
-        <v>39.28817914345438</v>
+        <v>523.5285714285715</v>
       </c>
       <c r="AY7" t="n">
-        <v>39.46203872077569</v>
+        <v>523.25625</v>
       </c>
       <c r="AZ7" t="n">
-        <v>39.70685017244863</v>
+        <v>524.1166666666667</v>
       </c>
       <c r="BA7" t="n">
-        <v>39.92508484649719</v>
+        <v>522.375</v>
       </c>
       <c r="BB7" t="n">
-        <v>447</v>
+        <v>51.61140862251291</v>
       </c>
       <c r="BC7" t="n">
-        <v>447</v>
+        <v>48.2495221622856</v>
       </c>
       <c r="BD7" t="n">
-        <v>447</v>
+        <v>46.84785047096612</v>
       </c>
       <c r="BE7" t="n">
-        <v>447</v>
+        <v>44.48662270840529</v>
       </c>
       <c r="BF7" t="n">
-        <v>447</v>
+        <v>43.80692407853149</v>
       </c>
       <c r="BG7" t="n">
-        <v>447</v>
+        <v>42.43254190176329</v>
       </c>
       <c r="BH7" t="n">
-        <v>447</v>
+        <v>41.98455770801331</v>
       </c>
       <c r="BI7" t="n">
-        <v>447</v>
+        <v>41.65230085681542</v>
       </c>
       <c r="BJ7" t="n">
-        <v>447</v>
+        <v>42.14017530813084</v>
       </c>
       <c r="BK7" t="n">
-        <v>646</v>
+        <v>437</v>
       </c>
       <c r="BL7" t="n">
-        <v>646</v>
+        <v>437</v>
       </c>
       <c r="BM7" t="n">
-        <v>646</v>
+        <v>437</v>
       </c>
       <c r="BN7" t="n">
-        <v>646</v>
+        <v>437</v>
       </c>
       <c r="BO7" t="n">
-        <v>646</v>
+        <v>437</v>
       </c>
       <c r="BP7" t="n">
-        <v>646</v>
+        <v>437</v>
       </c>
       <c r="BQ7" t="n">
-        <v>646</v>
+        <v>437</v>
       </c>
       <c r="BR7" t="n">
-        <v>646</v>
+        <v>437</v>
       </c>
       <c r="BS7" t="n">
-        <v>646</v>
+        <v>437</v>
       </c>
       <c r="BT7" t="n">
-        <v>1</v>
+        <v>643</v>
       </c>
       <c r="BU7" t="n">
-        <v>1</v>
+        <v>643</v>
       </c>
       <c r="BV7" t="n">
-        <v>1</v>
+        <v>643</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.9230769230769231</v>
+        <v>643</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.9411764705882353</v>
+        <v>643</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>643</v>
       </c>
       <c r="BZ7" t="n">
+        <v>643</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>643</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>643</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CI7" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="CA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>0</v>
+      <c r="CJ7" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>520.49</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>42.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S08_G8_520_41_ABS1</t>
+          <t>S07_G8_522_39_ABS1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C8" t="n">
-        <v>41</v>
+        <v>57.82060785767235</v>
       </c>
       <c r="D8" t="n">
-        <v>60.78576723498888</v>
+        <v>39</v>
       </c>
       <c r="E8" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F8" t="n">
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>514.6384169149195</v>
-      </c>
-      <c r="J8" t="n">
-        <v>41.26754536201434</v>
-      </c>
-      <c r="K8" t="n">
-        <v>512.8960955044611</v>
-      </c>
-      <c r="L8" t="n">
-        <v>40.55260611550834</v>
-      </c>
-      <c r="M8" t="n">
-        <v>519.152509541596</v>
-      </c>
-      <c r="N8" t="n">
-        <v>39.91912477904791</v>
-      </c>
-      <c r="O8" t="n">
-        <v>511.1060384157143</v>
-      </c>
-      <c r="P8" t="n">
-        <v>49.03123007645064</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>507.9899133508509</v>
-      </c>
       <c r="R8" t="n">
-        <v>51.15085685706607</v>
+        <v>538.24</v>
       </c>
       <c r="S8" t="n">
-        <v>511.9598487787543</v>
+        <v>39.33</v>
       </c>
       <c r="T8" t="n">
-        <v>53.58983714477671</v>
+        <v>523.6799999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>511.4834792055306</v>
+        <v>36.77</v>
       </c>
       <c r="V8" t="n">
-        <v>51.29874792004512</v>
+        <v>521.15</v>
       </c>
       <c r="W8" t="n">
-        <v>515.4923123984207</v>
+        <v>32.84</v>
       </c>
       <c r="X8" t="n">
-        <v>49.35632658713703</v>
+        <v>522.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>517.9104473956344</v>
+        <v>34.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>48.91212533683031</v>
+        <v>525.38</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.05</v>
+        <v>37.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.06666666666666667</v>
+        <v>526.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.075</v>
+        <v>38.46</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>521.62</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.03333333333333333</v>
+        <v>38.89</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>521.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.0125</v>
+        <v>37.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.01111111111111111</v>
+        <v>521.42</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.01</v>
+        <v>36.05</v>
       </c>
       <c r="AJ8" t="n">
-        <v>515.15</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="AK8" t="n">
-        <v>516.1333333333333</v>
+        <v>0.288135593220339</v>
       </c>
       <c r="AL8" t="n">
-        <v>516.6875</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="AM8" t="n">
-        <v>513.74</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="AN8" t="n">
-        <v>510.4</v>
+        <v>0.2100840336134454</v>
       </c>
       <c r="AO8" t="n">
-        <v>512.0857142857143</v>
+        <v>0.1942446043165468</v>
       </c>
       <c r="AP8" t="n">
-        <v>511.8</v>
+        <v>0.1446540880503145</v>
       </c>
       <c r="AQ8" t="n">
-        <v>512.0666666666667</v>
+        <v>0.1284916201117318</v>
       </c>
       <c r="AR8" t="n">
-        <v>512.625</v>
+        <v>0.135678391959799</v>
       </c>
       <c r="AS8" t="n">
-        <v>49.17090094761332</v>
+        <v>530.525</v>
       </c>
       <c r="AT8" t="n">
-        <v>47.52033482859967</v>
+        <v>528.3333333333334</v>
       </c>
       <c r="AU8" t="n">
-        <v>44.96876520152627</v>
+        <v>526.3375</v>
       </c>
       <c r="AV8" t="n">
-        <v>47.10872955196308</v>
+        <v>524.85</v>
       </c>
       <c r="AW8" t="n">
-        <v>50.17492733759894</v>
+        <v>524.775</v>
       </c>
       <c r="AX8" t="n">
-        <v>51.77816496697173</v>
+        <v>525.45</v>
       </c>
       <c r="AY8" t="n">
-        <v>51.8473480517567</v>
+        <v>524.48125</v>
       </c>
       <c r="AZ8" t="n">
-        <v>51.44107740361242</v>
+        <v>524.4444444444445</v>
       </c>
       <c r="BA8" t="n">
-        <v>50.84716683356114</v>
+        <v>524.37</v>
       </c>
       <c r="BB8" t="n">
-        <v>440</v>
+        <v>55.37507900671564</v>
       </c>
       <c r="BC8" t="n">
-        <v>440</v>
+        <v>50.38242638945537</v>
       </c>
       <c r="BD8" t="n">
-        <v>440</v>
+        <v>46.33032045809741</v>
       </c>
       <c r="BE8" t="n">
-        <v>440</v>
+        <v>44.67020819293324</v>
       </c>
       <c r="BF8" t="n">
-        <v>431</v>
+        <v>42.97101009207643</v>
       </c>
       <c r="BG8" t="n">
-        <v>431</v>
+        <v>42.51862197068144</v>
       </c>
       <c r="BH8" t="n">
-        <v>431</v>
+        <v>42.04283111824773</v>
       </c>
       <c r="BI8" t="n">
-        <v>431</v>
+        <v>41.80406974103814</v>
       </c>
       <c r="BJ8" t="n">
-        <v>431</v>
+        <v>40.93938323912562</v>
       </c>
       <c r="BK8" t="n">
-        <v>642</v>
+        <v>353</v>
       </c>
       <c r="BL8" t="n">
-        <v>642</v>
+        <v>353</v>
       </c>
       <c r="BM8" t="n">
-        <v>642</v>
+        <v>353</v>
       </c>
       <c r="BN8" t="n">
-        <v>642</v>
+        <v>353</v>
       </c>
       <c r="BO8" t="n">
-        <v>642</v>
+        <v>353</v>
       </c>
       <c r="BP8" t="n">
-        <v>642</v>
+        <v>353</v>
       </c>
       <c r="BQ8" t="n">
-        <v>642</v>
+        <v>353</v>
       </c>
       <c r="BR8" t="n">
-        <v>642</v>
+        <v>353</v>
       </c>
       <c r="BS8" t="n">
-        <v>642</v>
+        <v>353</v>
       </c>
       <c r="BT8" t="n">
-        <v>1</v>
+        <v>623</v>
       </c>
       <c r="BU8" t="n">
+        <v>623</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>623</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>623</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>623</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>623</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>623</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>623</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>623</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="CH8" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BV8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>0.7826086956521739</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>0.6896551724137931</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>0.7027027027027027</v>
+      <c r="CI8" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.813953488372093</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>521.42</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>36.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S07_G8_522_39_ABS1</t>
+          <t>S08_G8_520_41_ABS1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C9" t="n">
-        <v>39</v>
+        <v>60.78576723498888</v>
       </c>
       <c r="D9" t="n">
-        <v>57.82060785767235</v>
+        <v>41</v>
       </c>
       <c r="E9" t="n">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F9" t="n">
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>538.2389737123307</v>
-      </c>
-      <c r="J9" t="n">
-        <v>39.33122985867566</v>
-      </c>
-      <c r="K9" t="n">
-        <v>523.6796535759798</v>
-      </c>
-      <c r="L9" t="n">
-        <v>36.76640832236243</v>
-      </c>
-      <c r="M9" t="n">
-        <v>521.1479965547375</v>
-      </c>
-      <c r="N9" t="n">
-        <v>32.83602240202771</v>
-      </c>
-      <c r="O9" t="n">
-        <v>522.297782919469</v>
-      </c>
-      <c r="P9" t="n">
-        <v>34.16257629514759</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>525.3816899881969</v>
-      </c>
       <c r="R9" t="n">
-        <v>37.95985072012485</v>
+        <v>514.64</v>
       </c>
       <c r="S9" t="n">
-        <v>526.1259925210079</v>
+        <v>41.27</v>
       </c>
       <c r="T9" t="n">
-        <v>38.45733506568655</v>
+        <v>512.9</v>
       </c>
       <c r="U9" t="n">
-        <v>521.6167277631304</v>
+        <v>40.55</v>
       </c>
       <c r="V9" t="n">
-        <v>38.8895619514737</v>
+        <v>519.15</v>
       </c>
       <c r="W9" t="n">
-        <v>521.9534226761245</v>
+        <v>39.92</v>
       </c>
       <c r="X9" t="n">
-        <v>37.26181060775901</v>
+        <v>511.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>521.4152081489751</v>
+        <v>49.03</v>
       </c>
       <c r="Z9" t="n">
-        <v>36.05250519210678</v>
+        <v>507.99</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.3846153846153846</v>
+        <v>51.15</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.288135593220339</v>
+        <v>511.96</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.2658227848101266</v>
+        <v>53.59</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.2121212121212121</v>
+        <v>511.48</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.2100840336134454</v>
+        <v>51.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1942446043165468</v>
+        <v>515.49</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.1446540880503145</v>
+        <v>49.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.1284916201117318</v>
+        <v>517.91</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.135678391959799</v>
+        <v>48.91</v>
       </c>
       <c r="AJ9" t="n">
-        <v>530.525</v>
+        <v>0.05</v>
       </c>
       <c r="AK9" t="n">
-        <v>528.3333333333334</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="AL9" t="n">
-        <v>526.3375</v>
+        <v>0.075</v>
       </c>
       <c r="AM9" t="n">
-        <v>524.85</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>524.775</v>
+        <v>-0.03333333333333333</v>
       </c>
       <c r="AO9" t="n">
-        <v>525.45</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>524.48125</v>
+        <v>-0.0125</v>
       </c>
       <c r="AQ9" t="n">
-        <v>524.4444444444445</v>
+        <v>-0.01111111111111111</v>
       </c>
       <c r="AR9" t="n">
-        <v>524.37</v>
+        <v>-0.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>55.37507900671564</v>
+        <v>515.15</v>
       </c>
       <c r="AT9" t="n">
-        <v>50.38242638945537</v>
+        <v>516.1333333333333</v>
       </c>
       <c r="AU9" t="n">
-        <v>46.33032045809741</v>
+        <v>516.6875</v>
       </c>
       <c r="AV9" t="n">
-        <v>44.67020819293324</v>
+        <v>513.74</v>
       </c>
       <c r="AW9" t="n">
-        <v>42.97101009207643</v>
+        <v>510.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>42.51862197068144</v>
+        <v>512.0857142857143</v>
       </c>
       <c r="AY9" t="n">
-        <v>42.04283111824773</v>
+        <v>511.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>41.80406974103814</v>
+        <v>512.0666666666667</v>
       </c>
       <c r="BA9" t="n">
-        <v>40.93938323912562</v>
+        <v>512.625</v>
       </c>
       <c r="BB9" t="n">
-        <v>353</v>
+        <v>49.17090094761332</v>
       </c>
       <c r="BC9" t="n">
-        <v>353</v>
+        <v>47.52033482859967</v>
       </c>
       <c r="BD9" t="n">
-        <v>353</v>
+        <v>44.96876520152627</v>
       </c>
       <c r="BE9" t="n">
-        <v>353</v>
+        <v>47.10872955196308</v>
       </c>
       <c r="BF9" t="n">
-        <v>353</v>
+        <v>50.17492733759894</v>
       </c>
       <c r="BG9" t="n">
-        <v>353</v>
+        <v>51.77816496697173</v>
       </c>
       <c r="BH9" t="n">
-        <v>353</v>
+        <v>51.8473480517567</v>
       </c>
       <c r="BI9" t="n">
-        <v>353</v>
+        <v>51.44107740361242</v>
       </c>
       <c r="BJ9" t="n">
-        <v>353</v>
+        <v>50.84716683356114</v>
       </c>
       <c r="BK9" t="n">
-        <v>623</v>
+        <v>440</v>
       </c>
       <c r="BL9" t="n">
-        <v>623</v>
+        <v>440</v>
       </c>
       <c r="BM9" t="n">
-        <v>623</v>
+        <v>440</v>
       </c>
       <c r="BN9" t="n">
-        <v>623</v>
+        <v>440</v>
       </c>
       <c r="BO9" t="n">
-        <v>623</v>
+        <v>431</v>
       </c>
       <c r="BP9" t="n">
-        <v>623</v>
+        <v>431</v>
       </c>
       <c r="BQ9" t="n">
-        <v>623</v>
+        <v>431</v>
       </c>
       <c r="BR9" t="n">
-        <v>623</v>
+        <v>431</v>
       </c>
       <c r="BS9" t="n">
-        <v>623</v>
+        <v>431</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.8333333333333334</v>
+        <v>642</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.7272727272727273</v>
+        <v>642</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.9333333333333333</v>
+        <v>642</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.8947368421052632</v>
+        <v>642</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.9565217391304348</v>
+        <v>642</v>
       </c>
       <c r="BY9" t="n">
+        <v>642</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>642</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>642</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>642</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD9" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>0.0303030303030303</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.8421052631578947</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>0.813953488372093</v>
+      <c r="CE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.7826086956521739</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.7027027027027027</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>517.91</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>48.91</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>522</v>
       </c>
       <c r="C10" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D10" t="n">
         <v>41</v>
-      </c>
-      <c r="D10" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E10" t="n">
         <v>522</v>
@@ -2820,228 +3139,261 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>67</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>553.3929224967588</v>
-      </c>
-      <c r="J10" t="n">
-        <v>26.33506251474954</v>
-      </c>
-      <c r="K10" t="n">
-        <v>545.0664032939317</v>
-      </c>
-      <c r="L10" t="n">
-        <v>29.47545674035392</v>
-      </c>
-      <c r="M10" t="n">
-        <v>538.5955573909632</v>
-      </c>
-      <c r="N10" t="n">
-        <v>29.82794796339937</v>
-      </c>
-      <c r="O10" t="n">
-        <v>537.0930704940276</v>
-      </c>
-      <c r="P10" t="n">
-        <v>35.02830975173743</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>537.0245441425834</v>
-      </c>
       <c r="R10" t="n">
-        <v>39.58821000582444</v>
+        <v>553.39</v>
       </c>
       <c r="S10" t="n">
-        <v>538.1547691756077</v>
+        <v>26.34</v>
       </c>
       <c r="T10" t="n">
-        <v>38.08659765122982</v>
+        <v>545.0700000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>536.4484047228124</v>
+        <v>29.48</v>
       </c>
       <c r="V10" t="n">
-        <v>40.54776563199599</v>
+        <v>538.6</v>
       </c>
       <c r="W10" t="n">
-        <v>534.9574524814592</v>
+        <v>29.83</v>
       </c>
       <c r="X10" t="n">
-        <v>40.01027755609959</v>
+        <v>537.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>532.4099493199516</v>
+        <v>35.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>40.86726397196034</v>
+        <v>537.02</v>
       </c>
       <c r="AA10" t="n">
+        <v>39.59</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>538.15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>536.45</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>534.96</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>40.01</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>532.41</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>0.9</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AK10" t="n">
         <v>0.8</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AL10" t="n">
         <v>0.8</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AM10" t="n">
         <v>0.72</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AN10" t="n">
         <v>0.6833333333333333</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AO10" t="n">
         <v>0.5971223021582733</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AP10" t="n">
         <v>0.5443037974683544</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AQ10" t="n">
         <v>0.5028248587570622</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AR10" t="n">
         <v>0.4720812182741117</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AS10" t="n">
         <v>553.95</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>546.0833333333334</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>543.4125</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>541.05</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>540.3583333333333</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>539.8214285714286</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>539.0875</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>538.3944444444444</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>537.335</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>33.8119431562281</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>36.07228468259562</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>36.18518127286362</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>36.26523817652381</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>36.88671753565985</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>38.63866824404626</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>39.62218247080794</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>40.03269458583158</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>40.21184868916126</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>473</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>473</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>473</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>473</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>473</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>472</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>472</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>472</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>472</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BT10" t="n">
         <v>640</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BU10" t="n">
         <v>640</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BV10" t="n">
         <v>640</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BW10" t="n">
         <v>640</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BX10" t="n">
         <v>640</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BY10" t="n">
         <v>640</v>
       </c>
-      <c r="BQ10" t="n">
+      <c r="BZ10" t="n">
         <v>640</v>
       </c>
-      <c r="BR10" t="n">
+      <c r="CA10" t="n">
         <v>640</v>
       </c>
-      <c r="BS10" t="n">
+      <c r="CB10" t="n">
         <v>640</v>
       </c>
-      <c r="BT10" t="n">
+      <c r="CC10" t="n">
         <v>1</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.75</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.3125</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.2941176470588235</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.875</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>0.8846153846153846</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>532.41</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>40.87</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>518</v>
       </c>
       <c r="C11" t="n">
+        <v>59.30318754633062</v>
+      </c>
+      <c r="D11" t="n">
         <v>40</v>
-      </c>
-      <c r="D11" t="n">
-        <v>59.30318754633062</v>
       </c>
       <c r="E11" t="n">
         <v>518</v>
@@ -3066,228 +3418,261 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>512.3502013368151</v>
-      </c>
-      <c r="J11" t="n">
-        <v>75.26396533385865</v>
-      </c>
-      <c r="K11" t="n">
-        <v>519.3226984717776</v>
-      </c>
-      <c r="L11" t="n">
-        <v>59.31192685823319</v>
-      </c>
-      <c r="M11" t="n">
-        <v>527.0493499223397</v>
-      </c>
-      <c r="N11" t="n">
-        <v>56.10219981122751</v>
-      </c>
-      <c r="O11" t="n">
-        <v>529.907599555534</v>
-      </c>
-      <c r="P11" t="n">
-        <v>52.95454137167312</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>529.1810351603303</v>
-      </c>
       <c r="R11" t="n">
-        <v>52.85021641607741</v>
+        <v>512.35</v>
       </c>
       <c r="S11" t="n">
-        <v>529.2442432773736</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>52.86926310127431</v>
+        <v>519.3200000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>529.1160803883914</v>
+        <v>59.31</v>
       </c>
       <c r="V11" t="n">
-        <v>52.19398273029552</v>
+        <v>527.05</v>
       </c>
       <c r="W11" t="n">
-        <v>525.6981998499717</v>
+        <v>56.1</v>
       </c>
       <c r="X11" t="n">
-        <v>51.04141626593813</v>
+        <v>529.91</v>
       </c>
       <c r="Y11" t="n">
-        <v>526.4179864120113</v>
+        <v>52.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>52.28063890407119</v>
+        <v>529.1799999999999</v>
       </c>
       <c r="AA11" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>529.24</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>529.12</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>52.19</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>525.7</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>526.42</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>52.28</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>0.2</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AK11" t="n">
         <v>0.2</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AL11" t="n">
         <v>0.15</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AM11" t="n">
         <v>0.12</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AN11" t="n">
         <v>0.1</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AO11" t="n">
         <v>0.08571428571428572</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AP11" t="n">
         <v>0.075</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AQ11" t="n">
         <v>0.07777777777777778</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AR11" t="n">
         <v>0.06</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AS11" t="n">
         <v>511.775</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>517.6</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>519.1125</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>521.01</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>522</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>523.0857142857143</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>523.7375</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>524.6888888888889</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>524.515</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>61.15287707867881</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>64.56139197177625</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>62.32034052979813</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>61.60868364118812</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>59.01285170762947</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>58.55601539359991</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>57.0521129648149</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>55.81171610263375</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>54.74531737966271</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>401</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>401</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>401</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>401</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>401</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>401</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>401</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>401</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>401</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BT11" t="n">
         <v>632</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BU11" t="n">
         <v>632</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BV11" t="n">
         <v>632</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BW11" t="n">
         <v>632</v>
       </c>
-      <c r="BO11" t="n">
+      <c r="BX11" t="n">
         <v>632</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BY11" t="n">
         <v>632</v>
       </c>
-      <c r="BQ11" t="n">
+      <c r="BZ11" t="n">
         <v>632</v>
       </c>
-      <c r="BR11" t="n">
+      <c r="CA11" t="n">
         <v>632</v>
       </c>
-      <c r="BS11" t="n">
+      <c r="CB11" t="n">
         <v>632</v>
       </c>
-      <c r="BT11" t="n">
+      <c r="CC11" t="n">
         <v>0.75</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="CD11" t="n">
         <v>0</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>0</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>0.64</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CJ11" t="n">
         <v>0.7096774193548387</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CK11" t="n">
         <v>0.8181818181818182</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>526.42</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>52.28</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>521</v>
       </c>
       <c r="C12" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D12" t="n">
         <v>38</v>
-      </c>
-      <c r="D12" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E12" t="n">
         <v>521</v>
@@ -3312,228 +3697,261 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>517.5789420260641</v>
-      </c>
-      <c r="J12" t="n">
-        <v>32.06340970786994</v>
-      </c>
-      <c r="K12" t="n">
-        <v>522.773680215937</v>
-      </c>
-      <c r="L12" t="n">
-        <v>35.6018560109901</v>
-      </c>
-      <c r="M12" t="n">
-        <v>525.8354363293324</v>
-      </c>
-      <c r="N12" t="n">
-        <v>32.91706894858554</v>
-      </c>
-      <c r="O12" t="n">
-        <v>525.4709556247119</v>
-      </c>
-      <c r="P12" t="n">
-        <v>35.50459470929317</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>519.0267430029794</v>
-      </c>
       <c r="R12" t="n">
-        <v>37.46284927021181</v>
+        <v>517.58</v>
       </c>
       <c r="S12" t="n">
-        <v>515.4993260470595</v>
+        <v>32.06</v>
       </c>
       <c r="T12" t="n">
-        <v>40.34312966021982</v>
+        <v>522.77</v>
       </c>
       <c r="U12" t="n">
-        <v>514.5311902320979</v>
+        <v>35.6</v>
       </c>
       <c r="V12" t="n">
-        <v>40.6830783470003</v>
+        <v>525.84</v>
       </c>
       <c r="W12" t="n">
-        <v>514.6729259951043</v>
+        <v>32.92</v>
       </c>
       <c r="X12" t="n">
-        <v>38.5595549852253</v>
+        <v>525.47</v>
       </c>
       <c r="Y12" t="n">
-        <v>514.3745065066634</v>
+        <v>35.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>41.0375155324507</v>
+        <v>519.03</v>
       </c>
       <c r="AA12" t="n">
+        <v>37.46</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>515.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>514.53</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>514.67</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>514.37</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>0.35</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AK12" t="n">
         <v>0.3</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AL12" t="n">
         <v>0.2</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AM12" t="n">
         <v>0.2</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AN12" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AO12" t="n">
         <v>0.08571428571428572</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AP12" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AQ12" t="n">
         <v>0.07777777777777778</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AR12" t="n">
         <v>0.06</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AS12" t="n">
         <v>514.4</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>520.5166666666667</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>520.3375</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>521.03</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>519.8666666666667</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>517.7285714285714</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>516.60625</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>517.2</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>516.8049999999999</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>42.66661458330154</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>44.36533619342421</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>42.93219763475892</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>41.57269656878178</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>41.28618278418204</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>41.88212077744305</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>41.93344382396347</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>41.45873450392169</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>41.17762711716157</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>363</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>363</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>363</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>363</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>363</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>363</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>363</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>363</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>363</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BT12" t="n">
         <v>574</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BU12" t="n">
         <v>586</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BV12" t="n">
         <v>586</v>
       </c>
-      <c r="BN12" t="n">
+      <c r="BW12" t="n">
         <v>586</v>
       </c>
-      <c r="BO12" t="n">
+      <c r="BX12" t="n">
         <v>586</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BY12" t="n">
         <v>586</v>
       </c>
-      <c r="BQ12" t="n">
+      <c r="BZ12" t="n">
         <v>586</v>
       </c>
-      <c r="BR12" t="n">
+      <c r="CA12" t="n">
         <v>586</v>
       </c>
-      <c r="BS12" t="n">
+      <c r="CB12" t="n">
         <v>586</v>
       </c>
-      <c r="BT12" t="n">
+      <c r="CC12" t="n">
         <v>1</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>0.6842105263157895</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.8181818181818182</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.88</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.9642857142857143</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.9393939393939394</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>514.37</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>41.04</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>518</v>
       </c>
       <c r="C13" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E13" t="n">
         <v>518</v>
@@ -3558,720 +3976,819 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>503.1563079229173</v>
-      </c>
-      <c r="J13" t="n">
-        <v>32.49171817629308</v>
-      </c>
-      <c r="K13" t="n">
-        <v>497.8710403760189</v>
-      </c>
-      <c r="L13" t="n">
-        <v>41.39321938317014</v>
-      </c>
-      <c r="M13" t="n">
-        <v>500.1466557625732</v>
-      </c>
-      <c r="N13" t="n">
-        <v>44.44615609343536</v>
-      </c>
-      <c r="O13" t="n">
-        <v>502.1717590975892</v>
-      </c>
-      <c r="P13" t="n">
-        <v>45.25920041279843</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>505.8083942265428</v>
-      </c>
       <c r="R13" t="n">
-        <v>43.43601835884633</v>
+        <v>503.16</v>
       </c>
       <c r="S13" t="n">
-        <v>509.6076461037573</v>
+        <v>32.49</v>
       </c>
       <c r="T13" t="n">
-        <v>46.54145661590827</v>
+        <v>497.87</v>
       </c>
       <c r="U13" t="n">
-        <v>509.4759652130081</v>
+        <v>41.39</v>
       </c>
       <c r="V13" t="n">
-        <v>46.40032382852972</v>
+        <v>500.15</v>
       </c>
       <c r="W13" t="n">
-        <v>510.4513808453294</v>
+        <v>44.45</v>
       </c>
       <c r="X13" t="n">
-        <v>44.85617230311261</v>
+        <v>502.17</v>
       </c>
       <c r="Y13" t="n">
-        <v>510.139159582146</v>
+        <v>45.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>43.24546317209956</v>
+        <v>505.81</v>
       </c>
       <c r="AA13" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>509.61</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>509.48</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>510.45</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>510.14</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>0.1052631578947368</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AK13" t="n">
         <v>-0.03448275862068965</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AL13" t="n">
         <v>0</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AM13" t="n">
         <v>0.02040816326530612</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AN13" t="n">
         <v>0.01694915254237288</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AO13" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AP13" t="n">
         <v>0.0379746835443038</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AQ13" t="n">
         <v>0.03370786516853932</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AR13" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AS13" t="n">
         <v>509.05</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>499.15</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>500.85</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>502.52</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>502.7833333333334</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>505.1785714285714</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>505.59375</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>505.9166666666667</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>506.21</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>41.71087987563916</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>47.05699558337032</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>47.41336836800355</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>47.64587705143017</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>47.14979380183497</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>47.05897027850768</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>46.69934379557704</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>46.39359091273037</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>45.77483915864696</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>438</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>426</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>426</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>426</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>426</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>426</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>426</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>426</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>426</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BT13" t="n">
         <v>650</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BU13" t="n">
         <v>650</v>
       </c>
-      <c r="BM13" t="n">
+      <c r="BV13" t="n">
         <v>650</v>
       </c>
-      <c r="BN13" t="n">
+      <c r="BW13" t="n">
         <v>650</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BX13" t="n">
         <v>650</v>
       </c>
-      <c r="BP13" t="n">
+      <c r="BY13" t="n">
         <v>650</v>
       </c>
-      <c r="BQ13" t="n">
+      <c r="BZ13" t="n">
         <v>650</v>
       </c>
-      <c r="BR13" t="n">
+      <c r="CA13" t="n">
         <v>650</v>
       </c>
-      <c r="BS13" t="n">
+      <c r="CB13" t="n">
         <v>650</v>
       </c>
-      <c r="BT13" t="n">
+      <c r="CC13" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.875</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>0.65</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.696969696969697</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.7631578947368421</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>510.14</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>43.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S14_G8_522_39_ABS1</t>
+          <t>S13_G8_518_38_ABS1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>56.33802816901409</v>
       </c>
       <c r="D14" t="n">
-        <v>57.82060785767235</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F14" t="n">
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>515.3068295092097</v>
-      </c>
-      <c r="J14" t="n">
-        <v>27.27001968046355</v>
-      </c>
-      <c r="K14" t="n">
-        <v>520.6479702504163</v>
-      </c>
-      <c r="L14" t="n">
-        <v>40.75824187268117</v>
-      </c>
-      <c r="M14" t="n">
-        <v>524.7605033888761</v>
-      </c>
-      <c r="N14" t="n">
-        <v>39.24602126212542</v>
-      </c>
-      <c r="O14" t="n">
-        <v>526.3040720030352</v>
-      </c>
-      <c r="P14" t="n">
-        <v>36.6707958948339</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>522.7114879759049</v>
-      </c>
       <c r="R14" t="n">
-        <v>39.10577386247115</v>
+        <v>537.6900000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>521.1883029031499</v>
+        <v>33.36</v>
       </c>
       <c r="T14" t="n">
-        <v>43.86129344504539</v>
+        <v>523.74</v>
       </c>
       <c r="U14" t="n">
-        <v>519.3399548878107</v>
+        <v>67.84</v>
       </c>
       <c r="V14" t="n">
-        <v>42.65089449267451</v>
+        <v>520.9</v>
       </c>
       <c r="W14" t="n">
-        <v>518.4431160808103</v>
+        <v>59.9</v>
       </c>
       <c r="X14" t="n">
-        <v>46.63400526715713</v>
+        <v>516.99</v>
       </c>
       <c r="Y14" t="n">
-        <v>523.4185856657841</v>
+        <v>54.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>49.9099759161243</v>
+        <v>515.1900000000001</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.3157894736842105</v>
+        <v>51.23</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.3103448275862069</v>
+        <v>519.97</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.2564102564102564</v>
+        <v>53.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.2244897959183673</v>
+        <v>519.38</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.2203389830508475</v>
+        <v>51.32</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1449275362318841</v>
+        <v>517.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.1265822784810127</v>
+        <v>47.92</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.101123595505618</v>
+        <v>519.36</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.1212121212121212</v>
+        <v>46.99</v>
       </c>
       <c r="AJ14" t="n">
-        <v>512.1</v>
+        <v>0.95</v>
       </c>
       <c r="AK14" t="n">
-        <v>518.4333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AL14" t="n">
-        <v>520.7875</v>
+        <v>0.15</v>
       </c>
       <c r="AM14" t="n">
-        <v>522.85</v>
+        <v>0.06</v>
       </c>
       <c r="AN14" t="n">
-        <v>522.75</v>
+        <v>0.01666666666666667</v>
       </c>
       <c r="AO14" t="n">
-        <v>520.4428571428572</v>
+        <v>0.04285714285714286</v>
       </c>
       <c r="AP14" t="n">
-        <v>519.7625</v>
+        <v>0.025</v>
       </c>
       <c r="AQ14" t="n">
-        <v>518.9944444444444</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>520.71</v>
+        <v>-0.02</v>
       </c>
       <c r="AS14" t="n">
-        <v>43.64218143035474</v>
+        <v>546.575</v>
       </c>
       <c r="AT14" t="n">
-        <v>43.86812307612696</v>
+        <v>518.5833333333334</v>
       </c>
       <c r="AU14" t="n">
-        <v>45.27352806828732</v>
+        <v>511.6125</v>
       </c>
       <c r="AV14" t="n">
-        <v>44.52603171179754</v>
+        <v>510.92</v>
       </c>
       <c r="AW14" t="n">
-        <v>42.95991348532567</v>
+        <v>510.875</v>
       </c>
       <c r="AX14" t="n">
-        <v>43.55083588316588</v>
+        <v>513.9428571428572</v>
       </c>
       <c r="AY14" t="n">
-        <v>44.26376727923189</v>
+        <v>514.45</v>
       </c>
       <c r="AZ14" t="n">
-        <v>44.4832674187375</v>
+        <v>514.0944444444444</v>
       </c>
       <c r="BA14" t="n">
-        <v>45.18103473804025</v>
+        <v>514.02</v>
       </c>
       <c r="BB14" t="n">
-        <v>343</v>
+        <v>21.59153479954586</v>
       </c>
       <c r="BC14" t="n">
-        <v>343</v>
+        <v>48.28778025776523</v>
       </c>
       <c r="BD14" t="n">
-        <v>343</v>
+        <v>58.82675703920793</v>
       </c>
       <c r="BE14" t="n">
-        <v>343</v>
+        <v>58.7434558057321</v>
       </c>
       <c r="BF14" t="n">
-        <v>343</v>
+        <v>57.02186167018166</v>
       </c>
       <c r="BG14" t="n">
-        <v>343</v>
+        <v>56.98844136296054</v>
       </c>
       <c r="BH14" t="n">
-        <v>343</v>
+        <v>56.43434238121323</v>
       </c>
       <c r="BI14" t="n">
-        <v>343</v>
+        <v>55.1941721181002</v>
       </c>
       <c r="BJ14" t="n">
-        <v>343</v>
+        <v>53.84291596858402</v>
       </c>
       <c r="BK14" t="n">
-        <v>571</v>
+        <v>496</v>
       </c>
       <c r="BL14" t="n">
-        <v>592</v>
+        <v>436</v>
       </c>
       <c r="BM14" t="n">
-        <v>594</v>
+        <v>423</v>
       </c>
       <c r="BN14" t="n">
-        <v>594</v>
+        <v>423</v>
       </c>
       <c r="BO14" t="n">
-        <v>594</v>
+        <v>423</v>
       </c>
       <c r="BP14" t="n">
-        <v>594</v>
+        <v>423</v>
       </c>
       <c r="BQ14" t="n">
-        <v>594</v>
+        <v>423</v>
       </c>
       <c r="BR14" t="n">
-        <v>594</v>
+        <v>423</v>
       </c>
       <c r="BS14" t="n">
-        <v>594</v>
+        <v>423</v>
       </c>
       <c r="BT14" t="n">
+        <v>632</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>632</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>632</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>632</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>632</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>632</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>632</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>632</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>632</v>
+      </c>
+      <c r="CC14" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU14" t="n">
-        <v>0.6363636363636364</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>0.7727272727272727</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>0.9629629629629629</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>0.96875</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>0.9473684210526315</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>0.9285714285714286</v>
+      <c r="CD14" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.6206896551724138</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>519.36</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>46.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S13_G8_518_38_ABS1</t>
+          <t>S14_G8_522_39_ABS1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>57.82060785767235</v>
       </c>
       <c r="D15" t="n">
-        <v>56.33802816901409</v>
+        <v>39</v>
       </c>
       <c r="E15" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F15" t="n">
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>73.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>537.6875255379454</v>
-      </c>
-      <c r="J15" t="n">
-        <v>33.36261989236204</v>
-      </c>
-      <c r="K15" t="n">
-        <v>523.7412583179381</v>
-      </c>
-      <c r="L15" t="n">
-        <v>67.84301333467437</v>
-      </c>
-      <c r="M15" t="n">
-        <v>520.8954103564536</v>
-      </c>
-      <c r="N15" t="n">
-        <v>59.9040627091106</v>
-      </c>
-      <c r="O15" t="n">
-        <v>516.9916558646305</v>
-      </c>
-      <c r="P15" t="n">
-        <v>54.28660381575624</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>515.185943459565</v>
-      </c>
       <c r="R15" t="n">
-        <v>51.23177613399683</v>
+        <v>515.3099999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>519.968036743638</v>
+        <v>27.27</v>
       </c>
       <c r="T15" t="n">
-        <v>53.87662206029218</v>
+        <v>520.65</v>
       </c>
       <c r="U15" t="n">
-        <v>519.3818972401928</v>
+        <v>40.76</v>
       </c>
       <c r="V15" t="n">
-        <v>51.32025644509338</v>
+        <v>524.76</v>
       </c>
       <c r="W15" t="n">
-        <v>517.9013080300911</v>
+        <v>39.25</v>
       </c>
       <c r="X15" t="n">
-        <v>47.91513888182961</v>
+        <v>526.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>519.3627414486735</v>
+        <v>36.67</v>
       </c>
       <c r="Z15" t="n">
-        <v>46.99193527733952</v>
+        <v>522.71</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.95</v>
+        <v>39.11</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.3333333333333333</v>
+        <v>521.1900000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.15</v>
+        <v>43.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.06</v>
+        <v>519.34</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.01666666666666667</v>
+        <v>42.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.04285714285714286</v>
+        <v>518.4400000000001</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.025</v>
+        <v>46.63</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>523.42</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.02</v>
+        <v>49.91</v>
       </c>
       <c r="AJ15" t="n">
-        <v>546.575</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="AK15" t="n">
-        <v>518.5833333333334</v>
+        <v>0.3103448275862069</v>
       </c>
       <c r="AL15" t="n">
-        <v>511.6125</v>
+        <v>0.2564102564102564</v>
       </c>
       <c r="AM15" t="n">
-        <v>510.92</v>
+        <v>0.2244897959183673</v>
       </c>
       <c r="AN15" t="n">
-        <v>510.875</v>
+        <v>0.2203389830508475</v>
       </c>
       <c r="AO15" t="n">
-        <v>513.9428571428572</v>
+        <v>0.1449275362318841</v>
       </c>
       <c r="AP15" t="n">
-        <v>514.45</v>
+        <v>0.1265822784810127</v>
       </c>
       <c r="AQ15" t="n">
-        <v>514.0944444444444</v>
+        <v>0.101123595505618</v>
       </c>
       <c r="AR15" t="n">
-        <v>514.02</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="AS15" t="n">
-        <v>21.59153479954586</v>
+        <v>512.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>48.28778025776523</v>
+        <v>518.4333333333333</v>
       </c>
       <c r="AU15" t="n">
-        <v>58.82675703920793</v>
+        <v>520.7875</v>
       </c>
       <c r="AV15" t="n">
-        <v>58.7434558057321</v>
+        <v>522.85</v>
       </c>
       <c r="AW15" t="n">
-        <v>57.02186167018166</v>
+        <v>522.75</v>
       </c>
       <c r="AX15" t="n">
-        <v>56.98844136296054</v>
+        <v>520.4428571428572</v>
       </c>
       <c r="AY15" t="n">
-        <v>56.43434238121323</v>
+        <v>519.7625</v>
       </c>
       <c r="AZ15" t="n">
-        <v>55.1941721181002</v>
+        <v>518.9944444444444</v>
       </c>
       <c r="BA15" t="n">
-        <v>53.84291596858402</v>
+        <v>520.71</v>
       </c>
       <c r="BB15" t="n">
-        <v>496</v>
+        <v>43.64218143035474</v>
       </c>
       <c r="BC15" t="n">
-        <v>436</v>
+        <v>43.86812307612696</v>
       </c>
       <c r="BD15" t="n">
-        <v>423</v>
+        <v>45.27352806828732</v>
       </c>
       <c r="BE15" t="n">
-        <v>423</v>
+        <v>44.52603171179754</v>
       </c>
       <c r="BF15" t="n">
-        <v>423</v>
+        <v>42.95991348532567</v>
       </c>
       <c r="BG15" t="n">
-        <v>423</v>
+        <v>43.55083588316588</v>
       </c>
       <c r="BH15" t="n">
-        <v>423</v>
+        <v>44.26376727923189</v>
       </c>
       <c r="BI15" t="n">
-        <v>423</v>
+        <v>44.4832674187375</v>
       </c>
       <c r="BJ15" t="n">
-        <v>423</v>
+        <v>45.18103473804025</v>
       </c>
       <c r="BK15" t="n">
-        <v>632</v>
+        <v>343</v>
       </c>
       <c r="BL15" t="n">
-        <v>632</v>
+        <v>343</v>
       </c>
       <c r="BM15" t="n">
-        <v>632</v>
+        <v>343</v>
       </c>
       <c r="BN15" t="n">
-        <v>632</v>
+        <v>343</v>
       </c>
       <c r="BO15" t="n">
-        <v>632</v>
+        <v>343</v>
       </c>
       <c r="BP15" t="n">
-        <v>632</v>
+        <v>343</v>
       </c>
       <c r="BQ15" t="n">
-        <v>632</v>
+        <v>343</v>
       </c>
       <c r="BR15" t="n">
-        <v>632</v>
+        <v>343</v>
       </c>
       <c r="BS15" t="n">
-        <v>632</v>
+        <v>343</v>
       </c>
       <c r="BT15" t="n">
+        <v>571</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>592</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>594</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>594</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>594</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>594</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>594</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>594</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>594</v>
+      </c>
+      <c r="CC15" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU15" t="n">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>0.8421052631578947</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>0.6956521739130435</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>0.6206896551724138</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>0.6060606060606061</v>
+      <c r="CD15" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.96875</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>523.42</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>49.91</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>519</v>
       </c>
       <c r="C16" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D16" t="n">
         <v>42</v>
-      </c>
-      <c r="D16" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E16" t="n">
         <v>519</v>
@@ -4296,228 +4813,261 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>68</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>531.6320506548255</v>
-      </c>
-      <c r="J16" t="n">
-        <v>17.00319314147866</v>
-      </c>
-      <c r="K16" t="n">
-        <v>530.4413800167243</v>
-      </c>
-      <c r="L16" t="n">
-        <v>22.07680640731485</v>
-      </c>
-      <c r="M16" t="n">
-        <v>529.5929766635343</v>
-      </c>
-      <c r="N16" t="n">
-        <v>24.29755149696791</v>
-      </c>
-      <c r="O16" t="n">
-        <v>532.7114473465211</v>
-      </c>
-      <c r="P16" t="n">
-        <v>27.45629319949441</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>534.6693803512561</v>
-      </c>
       <c r="R16" t="n">
-        <v>26.98973472972169</v>
+        <v>531.63</v>
       </c>
       <c r="S16" t="n">
-        <v>525.8893362571649</v>
+        <v>17</v>
       </c>
       <c r="T16" t="n">
-        <v>37.24513786211191</v>
+        <v>530.4400000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>522.9926084489717</v>
+        <v>22.08</v>
       </c>
       <c r="V16" t="n">
-        <v>42.15815454650526</v>
+        <v>529.59</v>
       </c>
       <c r="W16" t="n">
-        <v>524.0676453090225</v>
+        <v>24.3</v>
       </c>
       <c r="X16" t="n">
-        <v>44.10074671102291</v>
+        <v>532.71</v>
       </c>
       <c r="Y16" t="n">
-        <v>523.7368311250732</v>
+        <v>27.46</v>
       </c>
       <c r="Z16" t="n">
-        <v>41.588906077118</v>
+        <v>534.67</v>
       </c>
       <c r="AA16" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>525.89</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>522.99</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>524.0700000000001</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>523.74</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>41.59</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>0.7435897435897436</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
         <v>0.7586206896551724</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AL16" t="n">
         <v>0.7435897435897436</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AM16" t="n">
         <v>0.7551020408163265</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AN16" t="n">
         <v>0.7435897435897436</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AO16" t="n">
         <v>0.6642335766423357</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AP16" t="n">
         <v>0.4522292993630573</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AQ16" t="n">
         <v>0.3898305084745763</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AR16" t="n">
         <v>0.350253807106599</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AS16" t="n">
         <v>532.25</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>533.9</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>531.375</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>535.11</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>536.3083333333333</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>532.2285714285714</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>525.3</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>524.2777777777778</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>523.855</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>29.42681600173556</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>27.96646801677561</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>27.90715634026513</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>29.57326326261612</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>30.09423971275714</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>31.09027014934389</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>34.53871016699958</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>36.80852189304289</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>38.74976096700469</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>466</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>466</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>466</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>466</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>466</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>466</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>461</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>458</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>457</v>
       </c>
-      <c r="BK16" t="n">
+      <c r="BT16" t="n">
         <v>645</v>
       </c>
-      <c r="BL16" t="n">
+      <c r="BU16" t="n">
         <v>645</v>
       </c>
-      <c r="BM16" t="n">
+      <c r="BV16" t="n">
         <v>645</v>
       </c>
-      <c r="BN16" t="n">
+      <c r="BW16" t="n">
         <v>645</v>
       </c>
-      <c r="BO16" t="n">
+      <c r="BX16" t="n">
         <v>645</v>
       </c>
-      <c r="BP16" t="n">
+      <c r="BY16" t="n">
         <v>645</v>
       </c>
-      <c r="BQ16" t="n">
+      <c r="BZ16" t="n">
         <v>645</v>
       </c>
-      <c r="BR16" t="n">
+      <c r="CA16" t="n">
         <v>645</v>
       </c>
-      <c r="BS16" t="n">
+      <c r="CB16" t="n">
         <v>645</v>
       </c>
-      <c r="BT16" t="n">
+      <c r="CC16" t="n">
         <v>1</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>1</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.7222222222222222</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.76</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.7142857142857143</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>523.74</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>41.59</v>
       </c>
     </row>
     <row r="17">
@@ -4530,10 +5080,10 @@
         <v>521</v>
       </c>
       <c r="C17" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D17" t="n">
         <v>41</v>
-      </c>
-      <c r="D17" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E17" t="n">
         <v>521</v>
@@ -4542,228 +5092,261 @@
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>73.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>522.9627164077812</v>
-      </c>
-      <c r="J17" t="n">
-        <v>20.01818575001534</v>
-      </c>
-      <c r="K17" t="n">
-        <v>512.4331447315429</v>
-      </c>
-      <c r="L17" t="n">
-        <v>37.01725201902162</v>
-      </c>
-      <c r="M17" t="n">
-        <v>510.5746969418516</v>
-      </c>
-      <c r="N17" t="n">
-        <v>31.39479485247564</v>
-      </c>
-      <c r="O17" t="n">
-        <v>514.4966856263389</v>
-      </c>
-      <c r="P17" t="n">
-        <v>38.83164479890443</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>519.545555491817</v>
-      </c>
       <c r="R17" t="n">
-        <v>54.17502851519735</v>
+        <v>522.96</v>
       </c>
       <c r="S17" t="n">
-        <v>518.5519522119702</v>
+        <v>20.02</v>
       </c>
       <c r="T17" t="n">
-        <v>51.32243750528647</v>
+        <v>512.4299999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>520.6902953230184</v>
+        <v>37.02</v>
       </c>
       <c r="V17" t="n">
-        <v>52.23683511609091</v>
+        <v>510.57</v>
       </c>
       <c r="W17" t="n">
-        <v>524.354707379122</v>
+        <v>31.39</v>
       </c>
       <c r="X17" t="n">
-        <v>51.5450190003577</v>
+        <v>514.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>523.6249196357775</v>
+        <v>38.83</v>
       </c>
       <c r="Z17" t="n">
-        <v>49.67292719511047</v>
+        <v>519.55</v>
       </c>
       <c r="AA17" t="n">
+        <v>54.18</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>518.55</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>51.32</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>520.6900000000001</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>524.35</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>523.62</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>0.95</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AK17" t="n">
         <v>0.5333333333333333</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AL17" t="n">
         <v>0.275</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AM17" t="n">
         <v>0.28</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AN17" t="n">
         <v>0.35</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AO17" t="n">
         <v>0.3285714285714286</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AP17" t="n">
         <v>0.3</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AQ17" t="n">
         <v>0.3</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AR17" t="n">
         <v>0.26</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AS17" t="n">
         <v>532.875</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AT17" t="n">
         <v>518.8333333333334</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AU17" t="n">
         <v>510.0875</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AV17" t="n">
         <v>513.84</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AW17" t="n">
         <v>521.9</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AX17" t="n">
         <v>523.3357142857143</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AY17" t="n">
         <v>523.3875</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AZ17" t="n">
         <v>525.1555555555556</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="BA17" t="n">
         <v>524.4450000000001</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="BB17" t="n">
         <v>32.73773625344306</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BC17" t="n">
         <v>36.49710795239656</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="BD17" t="n">
         <v>39.3291220821162</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="BE17" t="n">
         <v>39.29954707118137</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="BF17" t="n">
         <v>44.5144920222617</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="BG17" t="n">
         <v>49.6035152432748</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BH17" t="n">
         <v>51.30740535000771</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BI17" t="n">
         <v>51.90405916712768</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BJ17" t="n">
         <v>51.83432236462632</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BK17" t="n">
         <v>488</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BL17" t="n">
         <v>445</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BM17" t="n">
         <v>445</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BN17" t="n">
         <v>445</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BO17" t="n">
         <v>436</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BP17" t="n">
         <v>435</v>
       </c>
-      <c r="BH17" t="n">
+      <c r="BQ17" t="n">
         <v>435</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BR17" t="n">
         <v>435</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BS17" t="n">
         <v>435</v>
       </c>
-      <c r="BK17" t="n">
+      <c r="BT17" t="n">
         <v>652</v>
       </c>
-      <c r="BL17" t="n">
+      <c r="BU17" t="n">
         <v>652</v>
       </c>
-      <c r="BM17" t="n">
+      <c r="BV17" t="n">
         <v>652</v>
       </c>
-      <c r="BN17" t="n">
+      <c r="BW17" t="n">
         <v>652</v>
       </c>
-      <c r="BO17" t="n">
+      <c r="BX17" t="n">
         <v>652</v>
       </c>
-      <c r="BP17" t="n">
+      <c r="BY17" t="n">
         <v>652</v>
       </c>
-      <c r="BQ17" t="n">
+      <c r="BZ17" t="n">
         <v>652</v>
       </c>
-      <c r="BR17" t="n">
+      <c r="CA17" t="n">
         <v>652</v>
       </c>
-      <c r="BS17" t="n">
+      <c r="CB17" t="n">
         <v>652</v>
       </c>
-      <c r="BT17" t="n">
+      <c r="CC17" t="n">
         <v>0.4</v>
       </c>
-      <c r="BU17" t="n">
+      <c r="CD17" t="n">
         <v>0.3846153846153846</v>
       </c>
-      <c r="BV17" t="n">
+      <c r="CE17" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BW17" t="n">
+      <c r="CF17" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="CG17" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CH17" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CI17" t="n">
         <v>1</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CJ17" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CK17" t="n">
         <v>1</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>523.62</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>49.67</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>520</v>
       </c>
       <c r="C18" t="n">
+        <v>56.33802816901409</v>
+      </c>
+      <c r="D18" t="n">
         <v>38</v>
-      </c>
-      <c r="D18" t="n">
-        <v>56.33802816901409</v>
       </c>
       <c r="E18" t="n">
         <v>520</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>506.4106367126145</v>
-      </c>
-      <c r="J18" t="n">
-        <v>62.61155843847024</v>
-      </c>
-      <c r="K18" t="n">
-        <v>511.1610183835294</v>
-      </c>
-      <c r="L18" t="n">
-        <v>57.58163387254857</v>
-      </c>
-      <c r="M18" t="n">
-        <v>515.0813222054927</v>
-      </c>
-      <c r="N18" t="n">
-        <v>57.2273330336166</v>
-      </c>
-      <c r="O18" t="n">
-        <v>523.3881076675744</v>
-      </c>
-      <c r="P18" t="n">
-        <v>56.07039185866071</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>523.5976198337017</v>
-      </c>
       <c r="R18" t="n">
-        <v>55.13275764068354</v>
+        <v>506.41</v>
       </c>
       <c r="S18" t="n">
-        <v>521.8686584461245</v>
+        <v>62.61</v>
       </c>
       <c r="T18" t="n">
-        <v>50.17708793671388</v>
+        <v>511.16</v>
       </c>
       <c r="U18" t="n">
-        <v>520.2464936616602</v>
+        <v>57.58</v>
       </c>
       <c r="V18" t="n">
-        <v>51.89234055336479</v>
+        <v>515.08</v>
       </c>
       <c r="W18" t="n">
-        <v>518.1138745628022</v>
+        <v>57.23</v>
       </c>
       <c r="X18" t="n">
-        <v>50.07372363135403</v>
+        <v>523.39</v>
       </c>
       <c r="Y18" t="n">
-        <v>517.2661633588198</v>
+        <v>56.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>51.66487940830221</v>
+        <v>523.6</v>
       </c>
       <c r="AA18" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>521.87</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>520.25</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>51.89</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>518.11</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>517.27</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>0.15</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AK18" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AL18" t="n">
         <v>0.15</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AM18" t="n">
         <v>0.16</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AN18" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AO18" t="n">
         <v>0.08571428571428572</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AP18" t="n">
         <v>0.075</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AQ18" t="n">
         <v>0.07777777777777778</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AR18" t="n">
         <v>0.08</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AS18" t="n">
         <v>507.175</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>507.1333333333333</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>511.375</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>514.9400000000001</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>516.575</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>516.3857142857142</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>516.9125</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>517.5611111111111</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>517.8099999999999</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>45.27465488548753</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>53.05577777731239</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>57.37233109260944</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>57.87984450566536</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>58.23911378961736</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>56.94164753929935</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>55.5047731618642</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>54.67704818994376</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>53.69277325674285</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>435</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>418</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>418</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>418</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>418</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>418</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>418</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>418</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>418</v>
       </c>
-      <c r="BK18" t="n">
+      <c r="BT18" t="n">
         <v>630</v>
       </c>
-      <c r="BL18" t="n">
+      <c r="BU18" t="n">
         <v>630</v>
       </c>
-      <c r="BM18" t="n">
+      <c r="BV18" t="n">
         <v>630</v>
       </c>
-      <c r="BN18" t="n">
+      <c r="BW18" t="n">
         <v>630</v>
       </c>
-      <c r="BO18" t="n">
+      <c r="BX18" t="n">
         <v>630</v>
       </c>
-      <c r="BP18" t="n">
+      <c r="BY18" t="n">
         <v>630</v>
       </c>
-      <c r="BQ18" t="n">
+      <c r="BZ18" t="n">
         <v>630</v>
       </c>
-      <c r="BR18" t="n">
+      <c r="CA18" t="n">
         <v>630</v>
       </c>
-      <c r="BS18" t="n">
+      <c r="CB18" t="n">
         <v>630</v>
       </c>
-      <c r="BT18" t="n">
+      <c r="CC18" t="n">
         <v>1</v>
       </c>
-      <c r="BU18" t="n">
+      <c r="CD18" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="CF18" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="CG18" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
         <v>0.7826086956521739</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CI18" t="n">
         <v>0.8076923076923077</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CJ18" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CK18" t="n">
         <v>0.7428571428571429</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>517.27</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>51.66</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>522</v>
       </c>
       <c r="C19" t="n">
+        <v>62.26834692364714</v>
+      </c>
+      <c r="D19" t="n">
         <v>42</v>
-      </c>
-      <c r="D19" t="n">
-        <v>62.26834692364714</v>
       </c>
       <c r="E19" t="n">
         <v>522</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>524.6295912371252</v>
-      </c>
-      <c r="J19" t="n">
-        <v>71.81618092157123</v>
-      </c>
-      <c r="K19" t="n">
-        <v>531.4943450599196</v>
-      </c>
-      <c r="L19" t="n">
-        <v>55.12115429709137</v>
-      </c>
-      <c r="M19" t="n">
-        <v>525.2667961845053</v>
-      </c>
-      <c r="N19" t="n">
-        <v>53.93385542476491</v>
-      </c>
-      <c r="O19" t="n">
-        <v>525.8575565585912</v>
-      </c>
-      <c r="P19" t="n">
-        <v>48.66412650707252</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>521.5732050735661</v>
-      </c>
       <c r="R19" t="n">
-        <v>52.59789446564239</v>
+        <v>524.63</v>
       </c>
       <c r="S19" t="n">
-        <v>517.9065788372612</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>49.45031064080514</v>
+        <v>531.49</v>
       </c>
       <c r="U19" t="n">
-        <v>521.3659216220564</v>
+        <v>55.12</v>
       </c>
       <c r="V19" t="n">
-        <v>47.24121483454667</v>
+        <v>525.27</v>
       </c>
       <c r="W19" t="n">
-        <v>520.6464562721854</v>
+        <v>53.93</v>
       </c>
       <c r="X19" t="n">
-        <v>48.2352834666945</v>
+        <v>525.86</v>
       </c>
       <c r="Y19" t="n">
-        <v>523.8291444814207</v>
+        <v>48.66</v>
       </c>
       <c r="Z19" t="n">
-        <v>47.97767888273712</v>
+        <v>521.5700000000001</v>
       </c>
       <c r="AA19" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>517.91</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>521.37</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>47.24</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>520.65</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>523.83</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>0.45</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AK19" t="n">
         <v>0.2666666666666667</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AL19" t="n">
         <v>0.175</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AM19" t="n">
         <v>0.16</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AN19" t="n">
         <v>0.1</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AO19" t="n">
         <v>0.08571428571428572</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AP19" t="n">
         <v>0.08749999999999999</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AQ19" t="n">
         <v>0.08888888888888889</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AR19" t="n">
         <v>0.08</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AS19" t="n">
         <v>547.775</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>538</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>533.5875</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>532.1900000000001</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>529.35</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>527.8214285714286</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>527.05</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>526.7722222222222</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>526.075</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>61.5388038151539</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>61.94728942146433</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>61.55763432548395</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>58.83922076302507</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>57.47501631143744</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>56.92642718671969</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>55.31238559310202</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>53.95500497385201</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>53.01885867311744</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>465</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>446</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>446</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>446</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>446</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>446</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>446</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>446</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>446</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BT19" t="n">
         <v>722</v>
       </c>
-      <c r="BL19" t="n">
+      <c r="BU19" t="n">
         <v>722</v>
       </c>
-      <c r="BM19" t="n">
+      <c r="BV19" t="n">
         <v>722</v>
       </c>
-      <c r="BN19" t="n">
+      <c r="BW19" t="n">
         <v>722</v>
       </c>
-      <c r="BO19" t="n">
+      <c r="BX19" t="n">
         <v>722</v>
       </c>
-      <c r="BP19" t="n">
+      <c r="BY19" t="n">
         <v>722</v>
       </c>
-      <c r="BQ19" t="n">
+      <c r="BZ19" t="n">
         <v>722</v>
       </c>
-      <c r="BR19" t="n">
+      <c r="CA19" t="n">
         <v>722</v>
       </c>
-      <c r="BS19" t="n">
+      <c r="CB19" t="n">
         <v>722</v>
       </c>
-      <c r="BT19" t="n">
+      <c r="CC19" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.5</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.2631578947368421</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.6956521739130435</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.6428571428571429</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.6875</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.6944444444444444</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.7105263157894737</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.7674418604651163</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>523.83</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>47.98</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>520</v>
       </c>
       <c r="C20" t="n">
+        <v>60.78576723498888</v>
+      </c>
+      <c r="D20" t="n">
         <v>41</v>
-      </c>
-      <c r="D20" t="n">
-        <v>60.78576723498888</v>
       </c>
       <c r="E20" t="n">
         <v>520</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>537.1317074474651</v>
-      </c>
-      <c r="J20" t="n">
-        <v>81.62586908098108</v>
-      </c>
-      <c r="K20" t="n">
-        <v>536.6369756240294</v>
-      </c>
-      <c r="L20" t="n">
-        <v>76.18817132673317</v>
-      </c>
-      <c r="M20" t="n">
-        <v>532.8723712919715</v>
-      </c>
-      <c r="N20" t="n">
-        <v>68.23030199644532</v>
-      </c>
-      <c r="O20" t="n">
-        <v>533.9739701666616</v>
-      </c>
-      <c r="P20" t="n">
-        <v>62.80515636269634</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>531.5528272098661</v>
-      </c>
       <c r="R20" t="n">
-        <v>58.53062506873879</v>
+        <v>537.13</v>
       </c>
       <c r="S20" t="n">
-        <v>533.7215884575033</v>
+        <v>81.63</v>
       </c>
       <c r="T20" t="n">
-        <v>57.33690424112926</v>
+        <v>536.64</v>
       </c>
       <c r="U20" t="n">
-        <v>530.796695946464</v>
+        <v>76.19</v>
       </c>
       <c r="V20" t="n">
-        <v>57.53056080145104</v>
+        <v>532.87</v>
       </c>
       <c r="W20" t="n">
-        <v>529.0601608062811</v>
+        <v>68.23</v>
       </c>
       <c r="X20" t="n">
-        <v>54.60284620175729</v>
+        <v>533.97</v>
       </c>
       <c r="Y20" t="n">
-        <v>524.9081839017044</v>
+        <v>62.81</v>
       </c>
       <c r="Z20" t="n">
-        <v>54.0592013865551</v>
+        <v>531.55</v>
       </c>
       <c r="AA20" t="n">
+        <v>58.53</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>533.72</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>57.34</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>530.8</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>57.53</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>529.0599999999999</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>524.91</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>54.06</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AK20" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AL20" t="n">
         <v>0.25</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AM20" t="n">
         <v>0.22</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AN20" t="n">
         <v>0.1833333333333333</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AO20" t="n">
         <v>0.1654676258992806</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AP20" t="n">
         <v>0.1572327044025157</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AQ20" t="n">
         <v>0.1620111731843575</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AR20" t="n">
         <v>0.1658291457286432</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AS20" t="n">
         <v>537.35</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>536.7666666666667</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>536.65</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>536.54</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>535.9416666666667</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>535.5428571428571</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>535.475</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>535.5944444444444</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>535.475</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>54.56397621141626</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>64.6035000771802</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>67.83253275530851</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>67.0858286078364</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>65.20075355307551</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>62.7727615438156</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>61.58865053725403</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>60.29922583087173</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>58.57985468571939</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>441</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>441</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>441</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>441</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>441</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>441</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>441</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>441</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>441</v>
       </c>
-      <c r="BK20" t="n">
+      <c r="BT20" t="n">
         <v>644</v>
       </c>
-      <c r="BL20" t="n">
+      <c r="BU20" t="n">
         <v>644</v>
       </c>
-      <c r="BM20" t="n">
+      <c r="BV20" t="n">
         <v>644</v>
       </c>
-      <c r="BN20" t="n">
+      <c r="BW20" t="n">
         <v>644</v>
       </c>
-      <c r="BO20" t="n">
+      <c r="BX20" t="n">
         <v>644</v>
       </c>
-      <c r="BP20" t="n">
+      <c r="BY20" t="n">
         <v>644</v>
       </c>
-      <c r="BQ20" t="n">
+      <c r="BZ20" t="n">
         <v>644</v>
       </c>
-      <c r="BR20" t="n">
+      <c r="CA20" t="n">
         <v>644</v>
       </c>
-      <c r="BS20" t="n">
+      <c r="CB20" t="n">
         <v>644</v>
       </c>
-      <c r="BT20" t="n">
+      <c r="CC20" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>1</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>1</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.875</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.85</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.8</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.7857142857142857</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>524.91</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>54.06</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>520</v>
       </c>
       <c r="C21" t="n">
+        <v>57.82060785767235</v>
+      </c>
+      <c r="D21" t="n">
         <v>39</v>
-      </c>
-      <c r="D21" t="n">
-        <v>57.82060785767235</v>
       </c>
       <c r="E21" t="n">
         <v>520</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>ABS1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>518.4556213391442</v>
-      </c>
-      <c r="J21" t="n">
-        <v>62.32945309271662</v>
-      </c>
-      <c r="K21" t="n">
-        <v>528.4730899765556</v>
-      </c>
-      <c r="L21" t="n">
-        <v>63.09733667648606</v>
-      </c>
-      <c r="M21" t="n">
-        <v>529.1231630287099</v>
-      </c>
-      <c r="N21" t="n">
-        <v>55.16051241160795</v>
-      </c>
-      <c r="O21" t="n">
-        <v>533.905132429116</v>
-      </c>
-      <c r="P21" t="n">
-        <v>54.55868408792289</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>529.453730523826</v>
-      </c>
       <c r="R21" t="n">
-        <v>53.50619160305607</v>
+        <v>518.46</v>
       </c>
       <c r="S21" t="n">
-        <v>526.8825673016257</v>
+        <v>62.33</v>
       </c>
       <c r="T21" t="n">
-        <v>53.80306523979344</v>
+        <v>528.47</v>
       </c>
       <c r="U21" t="n">
-        <v>523.0227593188721</v>
+        <v>63.1</v>
       </c>
       <c r="V21" t="n">
-        <v>48.95768124586631</v>
+        <v>529.12</v>
       </c>
       <c r="W21" t="n">
-        <v>522.8203887654765</v>
+        <v>55.16</v>
       </c>
       <c r="X21" t="n">
-        <v>49.60940651337746</v>
+        <v>533.91</v>
       </c>
       <c r="Y21" t="n">
-        <v>520.7628442005306</v>
+        <v>54.56</v>
       </c>
       <c r="Z21" t="n">
-        <v>49.54128237465122</v>
+        <v>529.45</v>
       </c>
       <c r="AA21" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>526.88</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>523.02</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>522.8200000000001</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>520.76</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>0.2</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AK21" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AL21" t="n">
         <v>0.1139240506329114</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AM21" t="n">
         <v>0.09090909090909091</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AN21" t="n">
         <v>0.09243697478991597</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AO21" t="n">
         <v>0.07913669064748201</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AP21" t="n">
         <v>0.1069182389937107</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AQ21" t="n">
         <v>0.09497206703910614</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AR21" t="n">
         <v>0.09547738693467336</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AS21" t="n">
         <v>518.6</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>523.9</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>526.1125</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>526.8099999999999</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>529.4166666666666</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>528.6214285714286</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>529.76875</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>528.8833333333333</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>528.38</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>57.55944753035768</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>62.10198601225783</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>60.32018603875488</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>58.36449177368034</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>58.09899358470468</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>57.53600957625741</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>56.04230788821513</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>54.39825109525326</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>53.4233619309006</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>436</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>436</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>436</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>436</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>436</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>436</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>436</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>436</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>436</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BT21" t="n">
         <v>637</v>
       </c>
-      <c r="BL21" t="n">
+      <c r="BU21" t="n">
         <v>637</v>
       </c>
-      <c r="BM21" t="n">
+      <c r="BV21" t="n">
         <v>637</v>
       </c>
-      <c r="BN21" t="n">
+      <c r="BW21" t="n">
         <v>637</v>
       </c>
-      <c r="BO21" t="n">
+      <c r="BX21" t="n">
         <v>637</v>
       </c>
-      <c r="BP21" t="n">
+      <c r="BY21" t="n">
         <v>637</v>
       </c>
-      <c r="BQ21" t="n">
+      <c r="BZ21" t="n">
         <v>637</v>
       </c>
-      <c r="BR21" t="n">
+      <c r="CA21" t="n">
         <v>637</v>
       </c>
-      <c r="BS21" t="n">
+      <c r="CB21" t="n">
         <v>637</v>
       </c>
-      <c r="BT21" t="n">
+      <c r="CC21" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.75</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.631578947368421</v>
       </c>
-      <c r="BY21" t="n">
+      <c r="CH21" t="n">
         <v>0.75</v>
       </c>
-      <c r="BZ21" t="n">
+      <c r="CI21" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.95</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.9130434782608695</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>520.76</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>49.54</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>520</v>
       </c>
       <c r="C22" t="n">
+        <v>59.08080059303188</v>
+      </c>
+      <c r="D22" t="n">
         <v>39.85</v>
-      </c>
-      <c r="D22" t="n">
-        <v>59.08080059303188</v>
       </c>
       <c r="E22" t="n">
         <v>520</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5060000000000001</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>74.84999999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.7585</v>
+      </c>
       <c r="I22" t="n">
-        <v>524.4817454510061</v>
+        <v>2.7355</v>
       </c>
       <c r="J22" t="n">
-        <v>42.21945371771759</v>
+        <v>2.7135</v>
       </c>
       <c r="K22" t="n">
-        <v>523.0951378130719</v>
+        <v>2.688</v>
       </c>
       <c r="L22" t="n">
-        <v>44.52585328103219</v>
+        <v>2.662</v>
       </c>
       <c r="M22" t="n">
-        <v>522.8264055226812</v>
+        <v>2.6465</v>
       </c>
       <c r="N22" t="n">
-        <v>43.69591468318919</v>
+        <v>2.738999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>523.5623275668842</v>
+        <v>2.7695</v>
       </c>
       <c r="P22" t="n">
-        <v>44.21109592668251</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>523.2674856327169</v>
-      </c>
+        <v>2.76</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>44.97406162666709</v>
+        <v>524.4814999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>522.6418886953509</v>
+        <v>42.21900000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>46.10611214909648</v>
+        <v>523.0949999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>521.3053565005038</v>
+        <v>44.526</v>
       </c>
       <c r="V22" t="n">
-        <v>46.11255936994446</v>
+        <v>522.8265</v>
       </c>
       <c r="W22" t="n">
-        <v>521.1081071829195</v>
+        <v>43.697</v>
       </c>
       <c r="X22" t="n">
-        <v>45.12433128746506</v>
+        <v>523.5624999999999</v>
       </c>
       <c r="Y22" t="n">
-        <v>520.7992650691054</v>
+        <v>44.2115</v>
       </c>
       <c r="Z22" t="n">
-        <v>45.36676937161668</v>
+        <v>523.2675</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.4461808367071525</v>
+        <v>44.975</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.3466958893434638</v>
+        <v>522.6424999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.277993794180503</v>
+        <v>46.1065</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.2387162345100489</v>
+        <v>521.306</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.2174501282477354</v>
+        <v>46.1125</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.1920817477586141</v>
+        <v>521.1075</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.1623425185096728</v>
+        <v>45.1245</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.1478564858504088</v>
+        <v>520.7995</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.1349723831947514</v>
+        <v>45.367</v>
       </c>
       <c r="AJ22" t="n">
-        <v>527.2974999999999</v>
+        <v>0.446</v>
       </c>
       <c r="AK22" t="n">
-        <v>524.3966666666666</v>
+        <v>0.347</v>
       </c>
       <c r="AL22" t="n">
-        <v>522.6693749999999</v>
+        <v>0.2780000000000001</v>
       </c>
       <c r="AM22" t="n">
+        <v>0.2385</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0.2169999999999999</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0.1925</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.1355</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>527.2975</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>524.3965000000001</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>522.67</v>
+      </c>
+      <c r="AV22" t="n">
         <v>522.6125000000001</v>
       </c>
-      <c r="AN22" t="n">
-        <v>523.0495833333334</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>522.8278571428572</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>522.3084375</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>522.26</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>522.0945</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>44.7387510327021</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>47.34209670790282</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>48.02984130738359</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>48.10011286381608</v>
-      </c>
       <c r="AW22" t="n">
-        <v>48.08952518915055</v>
+        <v>523.0505000000001</v>
       </c>
       <c r="AX22" t="n">
-        <v>48.31862349444243</v>
+        <v>522.8285000000001</v>
       </c>
       <c r="AY22" t="n">
-        <v>48.16373113793372</v>
+        <v>522.3085</v>
       </c>
       <c r="AZ22" t="n">
-        <v>47.82798508410629</v>
+        <v>522.2594999999999</v>
       </c>
       <c r="BA22" t="n">
-        <v>47.40001650741215</v>
+        <v>522.0954999999999</v>
       </c>
       <c r="BB22" t="n">
+        <v>44.739</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>47.343</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>48.03000000000001</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>48.1005</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>48.0895</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>48.319</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>48.163</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>47.8275</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="BK22" t="n">
         <v>436.25</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>427.95</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>425.2</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>423.05</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>422.15</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>422.05</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>421.75</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>421.6</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>421.55</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>640.65</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>642.3</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>642.4</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>642.4</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>642.4</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>642.4</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>642.4</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>642.4</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>642.4</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.7716666666666667</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.6986409423909425</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.7695904899194373</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.6513228009595287</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.7152439967041527</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.7246532457075936</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.7799774981251283</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.83888166679788</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.7815260434879535</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>520.7995</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>45.367</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.450952500220023</v>
       </c>
       <c r="C23" t="n">
+        <v>1.940513828540445</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.308876577350532</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.940513828540445</v>
       </c>
       <c r="E23" t="n">
         <v>1.450952500220023</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01902906364375019</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>3.36428611337258</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1896610550151867</v>
+      </c>
       <c r="I23" t="n">
-        <v>13.75832637887058</v>
+        <v>0.2166606611853273</v>
       </c>
       <c r="J23" t="n">
-        <v>19.44276660508696</v>
+        <v>0.2376923044167551</v>
       </c>
       <c r="K23" t="n">
-        <v>12.07481758704225</v>
+        <v>0.2379429387589873</v>
       </c>
       <c r="L23" t="n">
-        <v>14.39696405093774</v>
+        <v>0.2342872730555151</v>
       </c>
       <c r="M23" t="n">
-        <v>9.19972073865056</v>
+        <v>0.2338527426889792</v>
       </c>
       <c r="N23" t="n">
-        <v>11.56118750189829</v>
+        <v>0.266021368354222</v>
       </c>
       <c r="O23" t="n">
-        <v>9.780633795802963</v>
+        <v>0.1944080082820935</v>
       </c>
       <c r="P23" t="n">
-        <v>9.4723916257207</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>9.06326764839651</v>
-      </c>
+        <v>0.1873077962240648</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>8.394724910496072</v>
+        <v>13.7576915425135</v>
       </c>
       <c r="S23" t="n">
-        <v>7.947407247431503</v>
+        <v>19.44353387308193</v>
       </c>
       <c r="T23" t="n">
-        <v>6.581967546813722</v>
+        <v>12.07568391873783</v>
       </c>
       <c r="U23" t="n">
-        <v>7.375982560059327</v>
+        <v>14.39612828067617</v>
       </c>
       <c r="V23" t="n">
-        <v>5.396768512813887</v>
+        <v>9.19985141470403</v>
       </c>
       <c r="W23" t="n">
-        <v>6.535421530864294</v>
+        <v>11.56018352613378</v>
       </c>
       <c r="X23" t="n">
-        <v>5.034869423317986</v>
+        <v>9.779764217909079</v>
       </c>
       <c r="Y23" t="n">
-        <v>6.201317907443356</v>
+        <v>9.472283265567912</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.878225989411721</v>
+        <v>9.06207822974979</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.3261230560658172</v>
+        <v>8.394574375593347</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.2845352661379581</v>
+        <v>7.946217819288559</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.2489947104593256</v>
+        <v>6.581590973073464</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.2165982236166369</v>
+        <v>7.376081116119784</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.2107225218052231</v>
+        <v>5.396484113705301</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.1845321158087462</v>
+        <v>6.535941018705723</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.1494219487823154</v>
+        <v>5.035548864664214</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.134627659419023</v>
+        <v>6.201944919900021</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.1240834184790942</v>
+        <v>4.877130411690012</v>
       </c>
       <c r="AJ23" t="n">
-        <v>16.31759403220954</v>
+        <v>0.3259867611131664</v>
       </c>
       <c r="AK23" t="n">
-        <v>13.72790686523567</v>
+        <v>0.2841441442944797</v>
       </c>
       <c r="AL23" t="n">
-        <v>11.84643133792109</v>
+        <v>0.2487569094517779</v>
       </c>
       <c r="AM23" t="n">
+        <v>0.2174075726178344</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0.2100651528003934</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.1840730690156551</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.1487350169366914</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.1343551851975713</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.1242440298258569</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>16.31813872093842</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>13.7280624135957</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>11.84596666869316</v>
+      </c>
+      <c r="AV23" t="n">
         <v>10.74375797969759</v>
       </c>
-      <c r="AN23" t="n">
-        <v>10.41422654753262</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>9.456932141077525</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>9.049750395247525</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>8.774036992525085</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>8.506753802900267</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>11.9815634044405</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>11.04008069349377</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>10.90066957987099</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.787724185139995</v>
-      </c>
       <c r="AW23" t="n">
-        <v>8.943470599992102</v>
+        <v>10.41403732569904</v>
       </c>
       <c r="AX23" t="n">
-        <v>8.21614696992687</v>
+        <v>9.456162165209349</v>
       </c>
       <c r="AY23" t="n">
-        <v>7.29979982248673</v>
+        <v>9.050573855025066</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6.604847901888724</v>
+        <v>8.772517777576432</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.962283878643504</v>
+        <v>8.50839552875185</v>
       </c>
       <c r="BB23" t="n">
+        <v>11.98158099575739</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>11.03925154785605</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>10.89993481390455</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>9.787705217314866</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>8.943510717127165</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>8.216555751715717</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>7.299731862415078</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>6.605284068954108</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>5.961813570771194</v>
+      </c>
+      <c r="BK23" t="n">
         <v>49.57596510194707</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>44.52849472085558</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>42.61405747798304</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>40.22106675022824</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>39.85668404619098</v>
       </c>
-      <c r="BG23" t="n">
-        <v>39.77234558941942</v>
-      </c>
-      <c r="BH23" t="n">
+      <c r="BP23" t="n">
+        <v>39.77234558941943</v>
+      </c>
+      <c r="BQ23" t="n">
         <v>39.44066162570913</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>39.28894313457132</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>39.24078839274525</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>35.15420915128986</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>32.02482589623573</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>31.86220331364421</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>31.86220331364421</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>31.86220331364421</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>31.86220331364421</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>31.86220331364421</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>31.86220331364421</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>31.86220331364421</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.2148098574409498</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.276647075699663</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.2482632218028228</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.2683527036155619</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.3028419637235898</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.2866193918244124</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.2429881132181201</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.1161441915646097</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.2302434264743301</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>6.201944919900021</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>4.877130411690012</v>
       </c>
     </row>
   </sheetData>
